--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,10 +547,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>16/09/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 7
+1 5 3 9
+5 8 9 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -558,14 +573,21 @@
 5 8 9 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 9/226 (3.98%)
+▶ Direct: 9/4302 (0.21%)
+▶ Total Sets hit: 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -573,7 +595,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -581,13 +603,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -595,7 +617,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -617,7 +639,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -639,7 +661,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -661,7 +683,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -683,7 +705,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -705,7 +727,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -727,7 +749,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -749,7 +771,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -771,7 +793,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -793,7 +815,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -815,7 +837,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -837,7 +859,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -859,7 +881,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -881,7 +903,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -903,7 +925,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -925,7 +947,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -947,7 +969,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -969,7 +991,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -991,7 +1013,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1013,7 +1035,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1035,7 +1057,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1057,7 +1079,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1079,7 +1101,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1101,7 +1123,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1123,7 +1145,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1145,7 +1167,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1189,7 +1211,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1233,7 +1255,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1255,7 +1277,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1277,7 +1299,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1299,7 +1321,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1321,7 +1343,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1343,7 +1365,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1365,7 +1387,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1387,7 +1409,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1409,7 +1431,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1431,7 +1453,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1453,7 +1475,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1475,7 +1497,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1497,7 +1519,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1519,7 +1541,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1541,7 +1563,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1563,7 +1585,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1585,7 +1607,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1607,7 +1629,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1629,7 +1651,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1651,7 +1673,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1673,7 +1695,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1695,7 +1717,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1805,7 +1827,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1827,7 +1849,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1849,7 +1871,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1871,7 +1893,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1893,7 +1915,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1915,7 +1937,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1937,7 +1959,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1959,7 +1981,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1981,7 +2003,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2003,7 +2025,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2025,7 +2047,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2047,7 +2069,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2069,7 +2091,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2091,7 +2113,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2113,7 +2135,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2135,7 +2157,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2157,7 +2179,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2179,7 +2201,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2201,7 +2223,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2223,7 +2245,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2245,7 +2267,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2267,7 +2289,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2289,7 +2311,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2311,7 +2333,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2333,7 +2355,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2355,7 +2377,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2377,7 +2399,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2399,7 +2421,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2421,7 +2443,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2443,7 +2465,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2465,7 +2487,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2487,7 +2509,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2509,7 +2531,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2531,7 +2553,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2553,7 +2575,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2575,7 +2597,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2597,7 +2619,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2619,7 +2641,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2641,7 +2663,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2663,7 +2685,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2685,7 +2707,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2707,7 +2729,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2729,7 +2751,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2751,7 +2773,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2773,7 +2795,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2795,7 +2817,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2817,7 +2839,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2839,7 +2861,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2861,7 +2883,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2883,7 +2905,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2905,7 +2927,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2927,7 +2949,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2949,7 +2971,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -2971,7 +2993,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3103,7 +3125,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3125,7 +3147,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3147,7 +3169,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3169,7 +3191,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3191,7 +3213,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3213,7 +3235,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3235,7 +3257,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3257,7 +3279,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3279,7 +3301,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3301,7 +3323,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3323,7 +3345,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3345,7 +3367,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3367,7 +3389,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3389,7 +3411,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3411,7 +3433,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3433,7 +3455,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3477,7 +3499,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3499,7 +3521,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3521,7 +3543,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3543,7 +3565,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3565,7 +3587,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B141" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3587,7 +3609,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3609,7 +3631,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3631,7 +3653,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3639,17 +3661,17 @@
         </is>
       </c>
     </row>
-    <row r="143" customHeight="1">
-      <c r="B143" s="4" t="n"/>
-      <c r="C143" s="1" t="n"/>
-    </row>
     <row r="144" customHeight="1">
-      <c r="B144" s="1" t="n"/>
+      <c r="B144" s="4" t="n"/>
       <c r="C144" s="1" t="n"/>
     </row>
     <row r="145" customHeight="1">
       <c r="B145" s="1" t="n"/>
       <c r="C145" s="1" t="n"/>
+    </row>
+    <row r="146" customHeight="1">
+      <c r="B146" s="1" t="n"/>
+      <c r="C146" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3662,7 +3684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3690,10 +3712,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13/09/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>1 0 7 7
+4 4 0 3
+9 6 6 9
+8 5 3 2</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 9/4176 (0.22%)
+✅ iBet: 9/220 (4.09%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -3701,20 +3744,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -3722,20 +3765,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -3743,20 +3786,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -3764,20 +3807,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -3785,20 +3828,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -3806,20 +3849,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -3827,20 +3870,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -3848,20 +3891,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -3869,20 +3912,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -3890,20 +3933,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -3911,20 +3954,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -3932,20 +3975,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -3953,20 +3996,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -3974,20 +4017,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -3995,20 +4038,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4016,20 +4059,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4037,20 +4080,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4058,20 +4101,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4079,20 +4122,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4100,20 +4143,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4121,20 +4164,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4142,20 +4185,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4163,20 +4206,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4184,20 +4227,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4205,20 +4248,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4226,20 +4269,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4247,20 +4290,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4268,20 +4311,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4289,20 +4332,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4310,20 +4353,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4331,20 +4374,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4352,20 +4395,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4373,20 +4416,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4394,20 +4437,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4415,20 +4458,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4436,20 +4479,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4457,20 +4500,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4478,20 +4521,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4499,20 +4542,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4520,20 +4563,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4541,20 +4584,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4562,20 +4605,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4583,20 +4626,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4604,20 +4647,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4625,20 +4668,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4646,20 +4689,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4667,20 +4710,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -4688,20 +4731,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -4709,20 +4752,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -4730,20 +4773,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -4751,20 +4794,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -4772,20 +4815,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -4793,20 +4836,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -4814,20 +4857,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -4835,20 +4878,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -4856,20 +4899,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -4877,20 +4920,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -4898,20 +4941,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -4919,20 +4962,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -4940,20 +4983,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -4961,20 +5004,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -4982,20 +5025,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5003,20 +5046,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5024,20 +5067,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5045,20 +5088,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5066,20 +5109,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5087,20 +5130,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5108,20 +5151,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5129,20 +5172,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5150,20 +5193,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5171,20 +5214,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5192,20 +5235,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5213,20 +5256,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5234,20 +5277,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5255,20 +5298,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5276,20 +5319,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5297,20 +5340,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5318,20 +5361,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5339,20 +5382,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5360,20 +5403,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5381,20 +5424,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5402,20 +5445,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5423,20 +5466,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5444,20 +5487,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5465,20 +5508,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5486,20 +5529,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5507,20 +5550,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5528,20 +5571,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5549,20 +5592,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5570,20 +5613,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5591,20 +5634,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5612,20 +5655,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5633,20 +5676,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5654,20 +5697,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -5675,20 +5718,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -5696,20 +5739,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -5717,20 +5760,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -5738,20 +5781,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -5759,20 +5802,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -5780,20 +5823,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -5801,20 +5844,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -5822,20 +5865,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -5843,20 +5886,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -5864,20 +5907,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -5885,20 +5928,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -5906,20 +5949,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -5927,20 +5970,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -5948,20 +5991,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -5969,20 +6012,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -5990,20 +6033,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6011,20 +6054,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6032,20 +6075,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6053,20 +6096,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6074,20 +6117,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6095,20 +6138,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6116,20 +6159,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6137,20 +6180,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6158,20 +6201,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6179,20 +6222,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6200,20 +6243,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6221,20 +6264,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6242,20 +6285,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6263,20 +6306,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6284,20 +6327,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6305,20 +6348,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6326,20 +6369,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6347,20 +6390,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6368,20 +6411,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6389,20 +6432,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6410,20 +6453,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6431,20 +6474,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6452,20 +6495,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6473,20 +6516,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6494,20 +6537,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6515,20 +6558,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6536,20 +6579,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6557,20 +6600,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6578,20 +6621,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B140" s="9" t="inlineStr">
+      <c r="B141" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6599,20 +6642,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B141" s="8" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6620,20 +6663,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B142" s="8" t="inlineStr">
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6641,20 +6684,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B143" s="8" t="inlineStr">
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -6662,20 +6705,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -6683,20 +6726,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -6704,20 +6747,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -6725,20 +6768,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -6746,20 +6789,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -6767,20 +6810,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -6788,20 +6831,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -6809,20 +6852,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -6830,20 +6873,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -6851,20 +6894,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -6872,20 +6915,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -6893,20 +6936,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -6914,20 +6957,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -6935,20 +6978,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -6956,20 +6999,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -6977,20 +7020,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -6998,20 +7041,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7019,20 +7062,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7040,20 +7083,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7061,20 +7104,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7082,20 +7125,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7103,20 +7146,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7124,20 +7167,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7145,20 +7188,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7166,20 +7209,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7187,20 +7230,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7208,20 +7251,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7229,20 +7272,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7250,20 +7293,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7271,20 +7314,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7292,20 +7335,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7313,20 +7356,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7334,20 +7377,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7355,20 +7398,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7376,20 +7419,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7397,20 +7440,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7418,20 +7461,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7439,20 +7482,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7460,20 +7503,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7481,20 +7524,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7502,20 +7545,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7523,20 +7566,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7544,20 +7587,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7565,20 +7608,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7586,20 +7629,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7607,20 +7650,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7628,20 +7671,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7649,20 +7692,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -7670,20 +7713,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -7691,20 +7734,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -7712,20 +7755,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -7733,20 +7776,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -7754,20 +7797,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -7775,16 +7818,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="197">
-      <c r="B197" s="1" t="n"/>
-      <c r="C197" s="1" t="n"/>
     </row>
     <row r="198">
       <c r="B198" s="1" t="n"/>
@@ -7796,6 +7835,7 @@
     </row>
     <row r="200">
       <c r="B200" s="1" t="n"/>
+      <c r="C200" s="1" t="n"/>
     </row>
     <row r="201">
       <c r="B201" s="1" t="n"/>
@@ -7871,6 +7911,9 @@
     </row>
     <row r="225">
       <c r="B225" s="1" t="n"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16/09/2026 (Wed)</t>
+          <t>19/09/2026 (Sat)</t>
         </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
@@ -562,10 +562,32 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>16/09/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 7
+1 5 3 9
+5 8 9 0</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 15/220 (6.82%)
+▶ Direct: 15/4176 (0.36%)
+▶ Total Sets hit: 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -573,7 +595,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -581,13 +603,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -595,7 +617,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -617,7 +639,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -639,7 +661,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -661,7 +683,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -683,7 +705,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -705,7 +727,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -727,7 +749,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -749,7 +771,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -771,7 +793,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -793,7 +815,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -815,7 +837,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -837,7 +859,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -859,7 +881,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -881,7 +903,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -903,7 +925,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -925,7 +947,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -947,7 +969,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -969,7 +991,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -991,7 +1013,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1013,7 +1035,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1035,7 +1057,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1057,7 +1079,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1079,7 +1101,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1101,7 +1123,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1123,7 +1145,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1145,7 +1167,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1255,7 +1277,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1277,7 +1299,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1299,7 +1321,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1321,7 +1343,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1343,7 +1365,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1365,7 +1387,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1387,7 +1409,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1409,7 +1431,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1431,7 +1453,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1453,7 +1475,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1475,7 +1497,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1497,7 +1519,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1519,7 +1541,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1541,7 +1563,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1563,7 +1585,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1585,7 +1607,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1607,7 +1629,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1629,7 +1651,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1651,7 +1673,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1673,7 +1695,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1695,7 +1717,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1827,7 +1849,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1849,7 +1871,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1871,7 +1893,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1893,7 +1915,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1915,7 +1937,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1937,7 +1959,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1959,7 +1981,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1981,7 +2003,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2003,7 +2025,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2025,7 +2047,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2047,7 +2069,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2069,7 +2091,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2091,7 +2113,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2113,7 +2135,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2135,7 +2157,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2157,7 +2179,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2179,7 +2201,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2201,7 +2223,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2223,7 +2245,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2245,7 +2267,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2267,7 +2289,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2289,7 +2311,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2311,7 +2333,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2333,7 +2355,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2355,7 +2377,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2377,7 +2399,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2399,7 +2421,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2421,7 +2443,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2443,7 +2465,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2465,7 +2487,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2487,7 +2509,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2509,7 +2531,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2531,7 +2553,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2553,7 +2575,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2575,7 +2597,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2597,7 +2619,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2619,7 +2641,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2641,7 +2663,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2663,7 +2685,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2685,7 +2707,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2707,7 +2729,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2729,7 +2751,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2751,7 +2773,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2773,7 +2795,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2795,7 +2817,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2817,7 +2839,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2839,7 +2861,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2861,7 +2883,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2883,7 +2905,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2905,7 +2927,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2927,7 +2949,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2949,7 +2971,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2971,7 +2993,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3103,7 +3125,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3125,7 +3147,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3147,7 +3169,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3169,7 +3191,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3191,7 +3213,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3213,7 +3235,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3235,7 +3257,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3257,7 +3279,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3279,7 +3301,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3301,7 +3323,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3323,7 +3345,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3345,7 +3367,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3367,7 +3389,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3389,7 +3411,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3411,7 +3433,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3433,7 +3455,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3477,7 +3499,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3499,7 +3521,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3521,7 +3543,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3543,7 +3565,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3565,7 +3587,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3587,7 +3609,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B141" s="7" t="inlineStr">
+      <c r="B142" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3609,7 +3631,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="B143" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3631,7 +3653,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3639,13 +3661,13 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3653,7 +3675,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3661,17 +3683,17 @@
         </is>
       </c>
     </row>
-    <row r="144" customHeight="1">
-      <c r="B144" s="4" t="n"/>
-      <c r="C144" s="1" t="n"/>
-    </row>
     <row r="145" customHeight="1">
-      <c r="B145" s="1" t="n"/>
+      <c r="B145" s="4" t="n"/>
       <c r="C145" s="1" t="n"/>
     </row>
     <row r="146" customHeight="1">
       <c r="B146" s="1" t="n"/>
       <c r="C146" s="1" t="n"/>
+    </row>
+    <row r="147" customHeight="1">
+      <c r="B147" s="1" t="n"/>
+      <c r="C147" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3684,7 +3706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C226"/>
+  <dimension ref="A1:C227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3712,10 +3734,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>16/09/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>6 7 1 1
+9 2 3 0
+8 4 7 8
+0 6 2 5</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 11/4230 (0.26%)
+✅ iBet: 11/221 (4.98%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>1 0 7 7
 4 4 0 3
@@ -3723,20 +3766,20 @@
 8 5 3 2</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4176 (0.22%)
 ✅ iBet: 9/220 (4.09%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -3744,20 +3787,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -3765,20 +3808,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -3786,20 +3829,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -3807,20 +3850,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -3828,20 +3871,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -3849,20 +3892,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -3870,20 +3913,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -3891,20 +3934,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -3912,20 +3955,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -3933,20 +3976,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -3954,20 +3997,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -3975,20 +4018,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -3996,20 +4039,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -4017,20 +4060,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -4038,20 +4081,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4059,20 +4102,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4080,20 +4123,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4101,20 +4144,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4122,20 +4165,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4143,20 +4186,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4164,20 +4207,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4185,20 +4228,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4206,20 +4249,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4227,20 +4270,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4248,20 +4291,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4269,20 +4312,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4290,20 +4333,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4311,20 +4354,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4332,20 +4375,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4353,20 +4396,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4374,20 +4417,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4395,20 +4438,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4416,20 +4459,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4437,20 +4480,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4458,20 +4501,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4479,20 +4522,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4500,20 +4543,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4521,20 +4564,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4542,20 +4585,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4563,20 +4606,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4584,20 +4627,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4605,20 +4648,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4626,20 +4669,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4647,20 +4690,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4668,20 +4711,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4689,20 +4732,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4710,20 +4753,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -4731,20 +4774,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -4752,20 +4795,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -4773,20 +4816,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -4794,20 +4837,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -4815,20 +4858,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -4836,20 +4879,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -4857,20 +4900,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -4878,20 +4921,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -4899,20 +4942,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -4920,20 +4963,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -4941,20 +4984,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -4962,20 +5005,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -4983,20 +5026,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -5004,20 +5047,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -5025,20 +5068,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5046,20 +5089,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5067,20 +5110,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5088,20 +5131,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5109,20 +5152,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5130,20 +5173,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5151,20 +5194,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5172,20 +5215,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5193,20 +5236,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5214,20 +5257,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5235,20 +5278,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5256,20 +5299,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5277,20 +5320,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5298,20 +5341,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5319,20 +5362,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5340,20 +5383,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5361,20 +5404,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5382,20 +5425,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5403,20 +5446,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5424,20 +5467,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5445,20 +5488,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5466,20 +5509,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5487,20 +5530,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5508,20 +5551,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5529,20 +5572,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5550,20 +5593,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5571,20 +5614,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5592,20 +5635,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5613,20 +5656,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5634,20 +5677,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5655,20 +5698,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5676,20 +5719,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5697,20 +5740,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -5718,20 +5761,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -5739,20 +5782,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -5760,20 +5803,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -5781,20 +5824,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -5802,20 +5845,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -5823,20 +5866,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -5844,20 +5887,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -5865,20 +5908,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -5886,20 +5929,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -5907,20 +5950,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -5928,20 +5971,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -5949,20 +5992,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -5970,20 +6013,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -5991,20 +6034,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -6012,20 +6055,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -6033,20 +6076,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6054,20 +6097,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6075,20 +6118,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6096,20 +6139,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6117,20 +6160,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6138,20 +6181,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6159,20 +6202,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6180,20 +6223,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6201,20 +6244,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6222,20 +6265,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6243,20 +6286,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6264,20 +6307,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6285,20 +6328,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6306,20 +6349,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6327,20 +6370,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6348,20 +6391,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6369,20 +6412,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6390,20 +6433,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6411,20 +6454,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6432,20 +6475,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6453,20 +6496,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6474,20 +6517,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6495,20 +6538,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6516,20 +6559,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6537,20 +6580,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6558,20 +6601,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6579,20 +6622,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6600,20 +6643,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6621,20 +6664,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B141" s="9" t="inlineStr">
+      <c r="B142" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6642,20 +6685,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B142" s="8" t="inlineStr">
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6663,20 +6706,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B143" s="8" t="inlineStr">
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6684,20 +6727,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -6705,20 +6748,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -6726,20 +6769,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -6747,20 +6790,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -6768,20 +6811,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -6789,20 +6832,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -6810,20 +6853,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -6831,20 +6874,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -6852,20 +6895,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -6873,20 +6916,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -6894,20 +6937,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -6915,20 +6958,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -6936,20 +6979,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -6957,20 +7000,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -6978,20 +7021,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -6999,20 +7042,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -7020,20 +7063,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -7041,20 +7084,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7062,20 +7105,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7083,20 +7126,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7104,20 +7147,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7125,20 +7168,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7146,20 +7189,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7167,20 +7210,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7188,20 +7231,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7209,20 +7252,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7230,20 +7273,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7251,20 +7294,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7272,20 +7315,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7293,20 +7336,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7314,20 +7357,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7335,20 +7378,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7356,20 +7399,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7377,20 +7420,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7398,20 +7441,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7419,20 +7462,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7440,20 +7483,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7461,20 +7504,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7482,20 +7525,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7503,20 +7546,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7524,20 +7567,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7545,20 +7588,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7566,20 +7609,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7587,20 +7630,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7608,20 +7651,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7629,20 +7672,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7650,20 +7693,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7671,20 +7714,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7692,20 +7735,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -7713,20 +7756,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -7734,20 +7777,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -7755,20 +7798,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -7776,20 +7819,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -7797,20 +7840,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
-      <c r="A197" t="inlineStr">
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -7818,16 +7861,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="198">
-      <c r="B198" s="1" t="n"/>
-      <c r="C198" s="1" t="n"/>
     </row>
     <row r="199">
       <c r="B199" s="1" t="n"/>
@@ -7839,6 +7878,7 @@
     </row>
     <row r="201">
       <c r="B201" s="1" t="n"/>
+      <c r="C201" s="1" t="n"/>
     </row>
     <row r="202">
       <c r="B202" s="1" t="n"/>
@@ -7914,6 +7954,9 @@
     </row>
     <row r="226">
       <c r="B226" s="1" t="n"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19/09/2026 (Sat)</t>
+          <t>20/09/2026 (Sun)</t>
         </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
@@ -562,7 +562,7 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16/09/2026 (Wed)</t>
+          <t>19/09/2026 (Sat)</t>
         </is>
       </c>
       <c r="B3" s="18" t="inlineStr">
@@ -575,19 +575,41 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>▶ iBet: 13/220 (5.91%)
+▶ Direct: 13/4176 (0.31%)
+▶ Total Sets hit: 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>16/09/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 7
+1 5 3 9
+5 8 9 0</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
           <t>▶ iBet: 15/220 (6.82%)
 ▶ Direct: 15/4176 (0.36%)
 ▶ Total Sets hit: 15</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -595,7 +617,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -617,7 +639,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -639,7 +661,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -661,7 +683,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -683,7 +705,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -705,7 +727,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -727,7 +749,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -749,7 +771,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -771,7 +793,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -793,7 +815,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -815,7 +837,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -837,7 +859,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -859,7 +881,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -881,7 +903,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -903,7 +925,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -925,7 +947,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -947,7 +969,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -969,7 +991,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -991,7 +1013,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1013,7 +1035,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1035,7 +1057,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1057,7 +1079,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1079,7 +1101,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1101,7 +1123,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1123,7 +1145,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1145,7 +1167,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1255,7 +1277,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1277,7 +1299,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1299,7 +1321,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1321,7 +1343,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1343,7 +1365,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1365,7 +1387,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1387,7 +1409,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1409,7 +1431,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1431,7 +1453,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1453,7 +1475,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1475,7 +1497,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1497,7 +1519,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1519,7 +1541,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1541,7 +1563,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1563,7 +1585,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1585,7 +1607,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1607,7 +1629,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1629,7 +1651,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1651,7 +1673,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1673,7 +1695,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1695,7 +1717,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1827,7 +1849,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1849,7 +1871,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1871,7 +1893,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1893,7 +1915,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1915,7 +1937,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1937,7 +1959,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1959,7 +1981,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1981,7 +2003,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2003,7 +2025,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2025,7 +2047,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2047,7 +2069,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2069,7 +2091,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2091,7 +2113,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2113,7 +2135,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2135,7 +2157,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2157,7 +2179,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2179,7 +2201,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2201,7 +2223,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2223,7 +2245,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2245,7 +2267,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2267,7 +2289,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2289,7 +2311,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2311,7 +2333,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2333,7 +2355,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2355,7 +2377,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2377,7 +2399,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2399,7 +2421,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2421,7 +2443,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2443,7 +2465,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2465,7 +2487,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2487,7 +2509,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2509,7 +2531,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2531,7 +2553,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2553,7 +2575,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2575,7 +2597,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2597,7 +2619,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2619,7 +2641,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2641,7 +2663,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2663,7 +2685,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2685,7 +2707,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2707,7 +2729,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2729,7 +2751,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2751,7 +2773,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2773,7 +2795,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2795,7 +2817,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2817,7 +2839,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2839,7 +2861,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2861,7 +2883,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2883,7 +2905,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2905,7 +2927,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2927,7 +2949,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2949,7 +2971,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2971,7 +2993,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3103,7 +3125,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3125,7 +3147,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3147,7 +3169,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3169,7 +3191,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3191,7 +3213,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3213,7 +3235,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3235,7 +3257,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3257,7 +3279,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3279,7 +3301,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3301,7 +3323,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3323,7 +3345,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3345,7 +3367,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3367,7 +3389,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3389,7 +3411,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3411,7 +3433,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3433,7 +3455,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3477,7 +3499,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3499,7 +3521,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3521,7 +3543,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3543,7 +3565,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3565,7 +3587,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
+      <c r="B141" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3587,7 +3609,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B141" s="10" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3609,7 +3631,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3631,7 +3653,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3639,13 +3661,13 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3653,7 +3675,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3661,13 +3683,13 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3675,7 +3697,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3683,17 +3705,17 @@
         </is>
       </c>
     </row>
-    <row r="145" customHeight="1">
-      <c r="B145" s="4" t="n"/>
-      <c r="C145" s="1" t="n"/>
-    </row>
     <row r="146" customHeight="1">
-      <c r="B146" s="1" t="n"/>
+      <c r="B146" s="4" t="n"/>
       <c r="C146" s="1" t="n"/>
     </row>
     <row r="147" customHeight="1">
       <c r="B147" s="1" t="n"/>
       <c r="C147" s="1" t="n"/>
+    </row>
+    <row r="148" customHeight="1">
+      <c r="B148" s="1" t="n"/>
+      <c r="C148" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3706,7 +3728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C227"/>
+  <dimension ref="A1:C228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3734,10 +3756,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>19/09/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>3 9 6 1
+7 0 3 5
+0 6 2 8
+4 2 1 4</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 10/4302 (0.23%)
+✅ iBet: 10/226 (4.42%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>6 7 1 1
 9 2 3 0
@@ -3745,20 +3788,20 @@
 0 6 2 5</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>1 0 7 7
 4 4 0 3
@@ -3766,20 +3809,20 @@
 8 5 3 2</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4176 (0.22%)
 ✅ iBet: 9/220 (4.09%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -3787,20 +3830,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -3808,20 +3851,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -3829,20 +3872,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -3850,20 +3893,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -3871,20 +3914,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -3892,20 +3935,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -3913,20 +3956,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -3934,20 +3977,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -3955,20 +3998,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -3976,20 +4019,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -3997,20 +4040,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -4018,20 +4061,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -4039,20 +4082,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -4060,20 +4103,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -4081,20 +4124,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4102,20 +4145,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4123,20 +4166,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4144,20 +4187,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4165,20 +4208,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4186,20 +4229,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4207,20 +4250,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4228,20 +4271,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4249,20 +4292,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4270,20 +4313,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4291,20 +4334,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4312,20 +4355,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4333,20 +4376,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4354,20 +4397,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4375,20 +4418,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4396,20 +4439,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4417,20 +4460,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4438,20 +4481,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4459,20 +4502,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4480,20 +4523,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4501,20 +4544,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4522,20 +4565,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4543,20 +4586,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4564,20 +4607,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4585,20 +4628,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4606,20 +4649,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4627,20 +4670,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4648,20 +4691,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4669,20 +4712,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4690,20 +4733,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4711,20 +4754,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4732,20 +4775,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4753,20 +4796,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -4774,20 +4817,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -4795,20 +4838,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -4816,20 +4859,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -4837,20 +4880,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -4858,20 +4901,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -4879,20 +4922,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -4900,20 +4943,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -4921,20 +4964,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -4942,20 +4985,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -4963,20 +5006,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -4984,20 +5027,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -5005,20 +5048,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -5026,20 +5069,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -5047,20 +5090,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -5068,20 +5111,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5089,20 +5132,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5110,20 +5153,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5131,20 +5174,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5152,20 +5195,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5173,20 +5216,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5194,20 +5237,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5215,20 +5258,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5236,20 +5279,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5257,20 +5300,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5278,20 +5321,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5299,20 +5342,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5320,20 +5363,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5341,20 +5384,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5362,20 +5405,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5383,20 +5426,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5404,20 +5447,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5425,20 +5468,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5446,20 +5489,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5467,20 +5510,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5488,20 +5531,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5509,20 +5552,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5530,20 +5573,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5551,20 +5594,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5572,20 +5615,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5593,20 +5636,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5614,20 +5657,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5635,20 +5678,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5656,20 +5699,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5677,20 +5720,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5698,20 +5741,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5719,20 +5762,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5740,20 +5783,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -5761,20 +5804,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -5782,20 +5825,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -5803,20 +5846,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -5824,20 +5867,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -5845,20 +5888,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -5866,20 +5909,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -5887,20 +5930,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -5908,20 +5951,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -5929,20 +5972,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -5950,20 +5993,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -5971,20 +6014,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -5992,20 +6035,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -6013,20 +6056,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -6034,20 +6077,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -6055,20 +6098,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -6076,20 +6119,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6097,20 +6140,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6118,20 +6161,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6139,20 +6182,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6160,20 +6203,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6181,20 +6224,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6202,20 +6245,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6223,20 +6266,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6244,20 +6287,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6265,20 +6308,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6286,20 +6329,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6307,20 +6350,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6328,20 +6371,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6349,20 +6392,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6370,20 +6413,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6391,20 +6434,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6412,20 +6455,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6433,20 +6476,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6454,20 +6497,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6475,20 +6518,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6496,20 +6539,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6517,20 +6560,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6538,20 +6581,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6559,20 +6602,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6580,20 +6623,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6601,20 +6644,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6622,20 +6665,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6643,20 +6686,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6664,20 +6707,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B142" s="9" t="inlineStr">
+      <c r="B143" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6685,20 +6728,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B143" s="8" t="inlineStr">
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6706,20 +6749,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6727,20 +6770,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -6748,20 +6791,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -6769,20 +6812,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -6790,20 +6833,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -6811,20 +6854,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -6832,20 +6875,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -6853,20 +6896,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -6874,20 +6917,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -6895,20 +6938,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -6916,20 +6959,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -6937,20 +6980,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -6958,20 +7001,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -6979,20 +7022,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -7000,20 +7043,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -7021,20 +7064,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -7042,20 +7085,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -7063,20 +7106,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -7084,20 +7127,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7105,20 +7148,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7126,20 +7169,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7147,20 +7190,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7168,20 +7211,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7189,20 +7232,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7210,20 +7253,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7231,20 +7274,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7252,20 +7295,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7273,20 +7316,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7294,20 +7337,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7315,20 +7358,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7336,20 +7379,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7357,20 +7400,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7378,20 +7421,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7399,20 +7442,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7420,20 +7463,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7441,20 +7484,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7462,20 +7505,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7483,20 +7526,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7504,20 +7547,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7525,20 +7568,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7546,20 +7589,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7567,20 +7610,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7588,20 +7631,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7609,20 +7652,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7630,20 +7673,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7651,20 +7694,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7672,20 +7715,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7693,20 +7736,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7714,20 +7757,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7735,20 +7778,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -7756,20 +7799,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -7777,20 +7820,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -7798,20 +7841,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -7819,20 +7862,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
-      <c r="A197" t="inlineStr">
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -7840,20 +7883,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="60" customHeight="1">
-      <c r="A198" t="inlineStr">
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -7861,16 +7904,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="199">
-      <c r="B199" s="1" t="n"/>
-      <c r="C199" s="1" t="n"/>
     </row>
     <row r="200">
       <c r="B200" s="1" t="n"/>
@@ -7882,6 +7921,7 @@
     </row>
     <row r="202">
       <c r="B202" s="1" t="n"/>
+      <c r="C202" s="1" t="n"/>
     </row>
     <row r="203">
       <c r="B203" s="1" t="n"/>
@@ -7957,6 +7997,9 @@
     </row>
     <row r="227">
       <c r="B227" s="1" t="n"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,10 +547,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23/09/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 7
+1 5 3 8
+5 8 9 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -558,14 +573,21 @@
 5 8 9 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 12/220 (5.45%)
+▶ Direct: 12/4176 (0.29%)
+▶ Total Sets hit: 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -573,7 +595,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/220 (5.91%)
 ▶ Direct: 13/4176 (0.31%)
@@ -581,13 +603,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -595,7 +617,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/220 (6.82%)
 ▶ Direct: 15/4176 (0.36%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -617,7 +639,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -639,7 +661,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -661,7 +683,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -683,7 +705,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -705,7 +727,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -727,7 +749,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -749,7 +771,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -771,7 +793,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -793,7 +815,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -815,7 +837,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -837,7 +859,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -859,7 +881,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -881,7 +903,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -903,7 +925,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -925,7 +947,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -947,7 +969,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -969,7 +991,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -991,7 +1013,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1013,7 +1035,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1035,7 +1057,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1057,7 +1079,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1079,7 +1101,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1101,7 +1123,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1123,7 +1145,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1145,7 +1167,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1255,7 +1277,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1277,7 +1299,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1299,7 +1321,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1321,7 +1343,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1343,7 +1365,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1365,7 +1387,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1387,7 +1409,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1409,7 +1431,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1431,7 +1453,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1453,7 +1475,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1475,7 +1497,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1497,7 +1519,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1519,7 +1541,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1541,7 +1563,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1563,7 +1585,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1585,7 +1607,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1607,7 +1629,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1629,7 +1651,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1651,7 +1673,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1673,7 +1695,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1695,7 +1717,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1827,7 +1849,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1849,7 +1871,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1871,7 +1893,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1893,7 +1915,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1915,7 +1937,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1937,7 +1959,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1959,7 +1981,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1981,7 +2003,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2003,7 +2025,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2025,7 +2047,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2047,7 +2069,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2069,7 +2091,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2091,7 +2113,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2113,7 +2135,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2135,7 +2157,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2157,7 +2179,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2179,7 +2201,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2201,7 +2223,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2223,7 +2245,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2245,7 +2267,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2267,7 +2289,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2289,7 +2311,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2311,7 +2333,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2333,7 +2355,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2355,7 +2377,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2377,7 +2399,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2399,7 +2421,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2421,7 +2443,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2443,7 +2465,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2465,7 +2487,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2487,7 +2509,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2509,7 +2531,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2531,7 +2553,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2553,7 +2575,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2575,7 +2597,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2597,7 +2619,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2619,7 +2641,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2641,7 +2663,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2663,7 +2685,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2685,7 +2707,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2707,7 +2729,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2729,7 +2751,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2751,7 +2773,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2773,7 +2795,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2795,7 +2817,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2817,7 +2839,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2839,7 +2861,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2861,7 +2883,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2883,7 +2905,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2905,7 +2927,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2927,7 +2949,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2949,7 +2971,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2971,7 +2993,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3103,7 +3125,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3125,7 +3147,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3147,7 +3169,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3169,7 +3191,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3191,7 +3213,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3213,7 +3235,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3235,7 +3257,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3257,7 +3279,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3279,7 +3301,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3301,7 +3323,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3323,7 +3345,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3345,7 +3367,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3367,7 +3389,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3389,7 +3411,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3411,7 +3433,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3433,7 +3455,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3477,7 +3499,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3499,7 +3521,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3521,7 +3543,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3543,7 +3565,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3565,7 +3587,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
+      <c r="B141" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3587,7 +3609,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B141" s="12" t="inlineStr">
+      <c r="B142" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3609,7 +3631,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B142" s="10" t="inlineStr">
+      <c r="B143" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3631,7 +3653,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3639,13 +3661,13 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B143" s="7" t="inlineStr">
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3653,7 +3675,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3661,13 +3683,13 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="B145" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3675,7 +3697,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3683,13 +3705,13 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3697,7 +3719,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3705,17 +3727,17 @@
         </is>
       </c>
     </row>
-    <row r="146" customHeight="1">
-      <c r="B146" s="4" t="n"/>
-      <c r="C146" s="1" t="n"/>
-    </row>
     <row r="147" customHeight="1">
-      <c r="B147" s="1" t="n"/>
+      <c r="B147" s="4" t="n"/>
       <c r="C147" s="1" t="n"/>
     </row>
     <row r="148" customHeight="1">
       <c r="B148" s="1" t="n"/>
       <c r="C148" s="1" t="n"/>
+    </row>
+    <row r="149" customHeight="1">
+      <c r="B149" s="1" t="n"/>
+      <c r="C149" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3728,7 +3750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C228"/>
+  <dimension ref="A1:C229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3756,10 +3778,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20/09/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>9 4 2 7
+3 3 9 1
+0 1 0 8
+7 6 5 2</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 15/4302 (0.35%)
+✅ iBet: 15/226 (6.64%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>3 9 6 1
 7 0 3 5
@@ -3767,20 +3810,20 @@
 4 2 1 4</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>6 7 1 1
 9 2 3 0
@@ -3788,20 +3831,20 @@
 0 6 2 5</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>1 0 7 7
 4 4 0 3
@@ -3809,20 +3852,20 @@
 8 5 3 2</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4176 (0.22%)
 ✅ iBet: 9/220 (4.09%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -3830,20 +3873,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -3851,20 +3894,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -3872,20 +3915,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -3893,20 +3936,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -3914,20 +3957,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -3935,20 +3978,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -3956,20 +3999,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -3977,20 +4020,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -3998,20 +4041,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -4019,20 +4062,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -4040,20 +4083,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -4061,20 +4104,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -4082,20 +4125,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -4103,20 +4146,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -4124,20 +4167,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4145,20 +4188,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4166,20 +4209,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4187,20 +4230,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4208,20 +4251,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4229,20 +4272,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4250,20 +4293,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4271,20 +4314,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4292,20 +4335,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4313,20 +4356,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4334,20 +4377,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4355,20 +4398,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4376,20 +4419,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4397,20 +4440,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4418,20 +4461,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4439,20 +4482,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4460,20 +4503,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4481,20 +4524,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4502,20 +4545,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4523,20 +4566,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4544,20 +4587,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4565,20 +4608,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4586,20 +4629,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4607,20 +4650,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4628,20 +4671,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4649,20 +4692,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4670,20 +4713,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4691,20 +4734,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4712,20 +4755,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4733,20 +4776,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4754,20 +4797,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4775,20 +4818,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4796,20 +4839,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -4817,20 +4860,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -4838,20 +4881,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -4859,20 +4902,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -4880,20 +4923,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -4901,20 +4944,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -4922,20 +4965,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -4943,20 +4986,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -4964,20 +5007,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -4985,20 +5028,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -5006,20 +5049,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -5027,20 +5070,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -5048,20 +5091,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -5069,20 +5112,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -5090,20 +5133,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -5111,20 +5154,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5132,20 +5175,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5153,20 +5196,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5174,20 +5217,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5195,20 +5238,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5216,20 +5259,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5237,20 +5280,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5258,20 +5301,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5279,20 +5322,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5300,20 +5343,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5321,20 +5364,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5342,20 +5385,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5363,20 +5406,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5384,20 +5427,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5405,20 +5448,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5426,20 +5469,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5447,20 +5490,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5468,20 +5511,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5489,20 +5532,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5510,20 +5553,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5531,20 +5574,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5552,20 +5595,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5573,20 +5616,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5594,20 +5637,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5615,20 +5658,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5636,20 +5679,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5657,20 +5700,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5678,20 +5721,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5699,20 +5742,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5720,20 +5763,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5741,20 +5784,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5762,20 +5805,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5783,20 +5826,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -5804,20 +5847,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -5825,20 +5868,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -5846,20 +5889,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -5867,20 +5910,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -5888,20 +5931,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -5909,20 +5952,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -5930,20 +5973,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -5951,20 +5994,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -5972,20 +6015,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -5993,20 +6036,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -6014,20 +6057,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -6035,20 +6078,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -6056,20 +6099,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -6077,20 +6120,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -6098,20 +6141,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -6119,20 +6162,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6140,20 +6183,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6161,20 +6204,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6182,20 +6225,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6203,20 +6246,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6224,20 +6267,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6245,20 +6288,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6266,20 +6309,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6287,20 +6330,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6308,20 +6351,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6329,20 +6372,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6350,20 +6393,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6371,20 +6414,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6392,20 +6435,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6413,20 +6456,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6434,20 +6477,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6455,20 +6498,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6476,20 +6519,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6497,20 +6540,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6518,20 +6561,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6539,20 +6582,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6560,20 +6603,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6581,20 +6624,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6602,20 +6645,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6623,20 +6666,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6644,20 +6687,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6665,20 +6708,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6686,20 +6729,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6707,20 +6750,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B143" s="9" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6728,20 +6771,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6749,20 +6792,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6770,20 +6813,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -6791,20 +6834,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -6812,20 +6855,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -6833,20 +6876,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -6854,20 +6897,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -6875,20 +6918,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -6896,20 +6939,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -6917,20 +6960,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -6938,20 +6981,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -6959,20 +7002,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -6980,20 +7023,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -7001,20 +7044,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -7022,20 +7065,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -7043,20 +7086,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -7064,20 +7107,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -7085,20 +7128,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -7106,20 +7149,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -7127,20 +7170,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7148,20 +7191,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7169,20 +7212,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7190,20 +7233,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7211,20 +7254,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7232,20 +7275,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7253,20 +7296,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7274,20 +7317,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7295,20 +7338,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7316,20 +7359,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7337,20 +7380,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7358,20 +7401,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7379,20 +7422,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7400,20 +7443,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7421,20 +7464,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7442,20 +7485,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7463,20 +7506,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7484,20 +7527,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7505,20 +7548,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7526,20 +7569,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7547,20 +7590,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7568,20 +7611,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7589,20 +7632,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7610,20 +7653,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7631,20 +7674,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7652,20 +7695,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7673,20 +7716,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7694,20 +7737,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7715,20 +7758,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7736,20 +7779,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7757,20 +7800,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7778,20 +7821,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -7799,20 +7842,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -7820,20 +7863,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -7841,20 +7884,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
-      <c r="A197" t="inlineStr">
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -7862,20 +7905,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="60" customHeight="1">
-      <c r="A198" t="inlineStr">
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -7883,20 +7926,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="60" customHeight="1">
-      <c r="A199" t="inlineStr">
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B199" s="8" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -7904,16 +7947,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C199" s="1" t="inlineStr">
+      <c r="C200" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="200">
-      <c r="B200" s="1" t="n"/>
-      <c r="C200" s="1" t="n"/>
     </row>
     <row r="201">
       <c r="B201" s="1" t="n"/>
@@ -7925,6 +7964,7 @@
     </row>
     <row r="203">
       <c r="B203" s="1" t="n"/>
+      <c r="C203" s="1" t="n"/>
     </row>
     <row r="204">
       <c r="B204" s="1" t="n"/>
@@ -8000,6 +8040,9 @@
     </row>
     <row r="228">
       <c r="B228" s="1" t="n"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,10 +547,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>26/09/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>0 7 1 6
+3 2 6 5
+1 5 3 8
+4 8 9 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -558,14 +573,21 @@
 5 8 9 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 10/221 (4.52%)
+▶ Direct: 10/4230 (0.24%)
+▶ Total Sets hit: 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -573,7 +595,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -581,13 +603,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -595,7 +617,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/220 (5.91%)
 ▶ Direct: 13/4176 (0.31%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -617,7 +639,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/220 (6.82%)
 ▶ Direct: 15/4176 (0.36%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -639,7 +661,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -661,7 +683,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -683,7 +705,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -705,7 +727,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -727,7 +749,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -749,7 +771,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -771,7 +793,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -793,7 +815,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -815,7 +837,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -837,7 +859,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -859,7 +881,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -881,7 +903,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -903,7 +925,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -925,7 +947,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -947,7 +969,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -969,7 +991,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -991,7 +1013,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1013,7 +1035,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1035,7 +1057,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1057,7 +1079,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1079,7 +1101,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1101,7 +1123,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1123,7 +1145,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1145,7 +1167,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1255,7 +1277,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1277,7 +1299,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1299,7 +1321,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1321,7 +1343,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1343,7 +1365,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1365,7 +1387,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1387,7 +1409,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1409,7 +1431,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1431,7 +1453,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1453,7 +1475,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1475,7 +1497,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1497,7 +1519,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1519,7 +1541,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1541,7 +1563,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1563,7 +1585,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1585,7 +1607,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1607,7 +1629,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1629,7 +1651,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1651,7 +1673,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1673,7 +1695,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1695,7 +1717,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1827,7 +1849,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1849,7 +1871,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1871,7 +1893,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1893,7 +1915,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1915,7 +1937,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1937,7 +1959,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1959,7 +1981,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1981,7 +2003,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2003,7 +2025,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2025,7 +2047,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2047,7 +2069,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2069,7 +2091,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2091,7 +2113,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2113,7 +2135,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2135,7 +2157,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2157,7 +2179,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2179,7 +2201,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2201,7 +2223,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2223,7 +2245,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2245,7 +2267,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2267,7 +2289,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2289,7 +2311,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2311,7 +2333,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2333,7 +2355,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2355,7 +2377,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2377,7 +2399,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2399,7 +2421,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2421,7 +2443,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2443,7 +2465,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2465,7 +2487,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2487,7 +2509,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2509,7 +2531,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2531,7 +2553,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2553,7 +2575,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2575,7 +2597,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2597,7 +2619,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2619,7 +2641,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2641,7 +2663,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2663,7 +2685,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2685,7 +2707,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2707,7 +2729,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2729,7 +2751,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2751,7 +2773,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2773,7 +2795,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2795,7 +2817,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2817,7 +2839,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2839,7 +2861,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2861,7 +2883,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2883,7 +2905,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2905,7 +2927,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2927,7 +2949,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2949,7 +2971,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2971,7 +2993,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3103,7 +3125,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3125,7 +3147,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3147,7 +3169,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3169,7 +3191,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3191,7 +3213,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3213,7 +3235,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3235,7 +3257,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3257,7 +3279,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3279,7 +3301,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3301,7 +3323,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3323,7 +3345,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3345,7 +3367,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3367,7 +3389,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3389,7 +3411,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3411,7 +3433,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3433,7 +3455,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3477,7 +3499,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3499,7 +3521,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3521,7 +3543,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3543,7 +3565,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3565,7 +3587,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
+      <c r="B141" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3587,7 +3609,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B141" s="12" t="inlineStr">
+      <c r="B142" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3609,7 +3631,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B142" s="12" t="inlineStr">
+      <c r="B143" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3631,7 +3653,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3639,13 +3661,13 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B143" s="10" t="inlineStr">
+      <c r="B144" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3653,7 +3675,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3661,13 +3683,13 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3675,7 +3697,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3683,13 +3705,13 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3697,7 +3719,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3705,13 +3727,13 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3719,7 +3741,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3727,17 +3749,17 @@
         </is>
       </c>
     </row>
-    <row r="147" customHeight="1">
-      <c r="B147" s="4" t="n"/>
-      <c r="C147" s="1" t="n"/>
-    </row>
     <row r="148" customHeight="1">
-      <c r="B148" s="1" t="n"/>
+      <c r="B148" s="4" t="n"/>
       <c r="C148" s="1" t="n"/>
     </row>
     <row r="149" customHeight="1">
       <c r="B149" s="1" t="n"/>
       <c r="C149" s="1" t="n"/>
+    </row>
+    <row r="150" customHeight="1">
+      <c r="B150" s="1" t="n"/>
+      <c r="C150" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3750,7 +3772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C229"/>
+  <dimension ref="A1:C230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3778,10 +3800,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23/09/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>1 8 7 4
+0 5 9 5
+6 2 0 3
+9 4 8 7</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 9/4128 (0.22%)
+✅ iBet: 9/217 (4.15%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>9 4 2 7
 3 3 9 1
@@ -3789,20 +3832,20 @@
 7 6 5 2</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>3 9 6 1
 7 0 3 5
@@ -3810,20 +3853,20 @@
 4 2 1 4</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>6 7 1 1
 9 2 3 0
@@ -3831,20 +3874,20 @@
 0 6 2 5</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>1 0 7 7
 4 4 0 3
@@ -3852,20 +3895,20 @@
 8 5 3 2</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4176 (0.22%)
 ✅ iBet: 9/220 (4.09%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -3873,20 +3916,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -3894,20 +3937,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -3915,20 +3958,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -3936,20 +3979,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -3957,20 +4000,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -3978,20 +4021,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -3999,20 +4042,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -4020,20 +4063,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -4041,20 +4084,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -4062,20 +4105,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -4083,20 +4126,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -4104,20 +4147,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -4125,20 +4168,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -4146,20 +4189,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -4167,20 +4210,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4188,20 +4231,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4209,20 +4252,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4230,20 +4273,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4251,20 +4294,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4272,20 +4315,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4293,20 +4336,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4314,20 +4357,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4335,20 +4378,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4356,20 +4399,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4377,20 +4420,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4398,20 +4441,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4419,20 +4462,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4440,20 +4483,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4461,20 +4504,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4482,20 +4525,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4503,20 +4546,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4524,20 +4567,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4545,20 +4588,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4566,20 +4609,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4587,20 +4630,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4608,20 +4651,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4629,20 +4672,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4650,20 +4693,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4671,20 +4714,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4692,20 +4735,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4713,20 +4756,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4734,20 +4777,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4755,20 +4798,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4776,20 +4819,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4797,20 +4840,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4818,20 +4861,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4839,20 +4882,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -4860,20 +4903,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -4881,20 +4924,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -4902,20 +4945,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -4923,20 +4966,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -4944,20 +4987,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -4965,20 +5008,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -4986,20 +5029,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -5007,20 +5050,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -5028,20 +5071,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -5049,20 +5092,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -5070,20 +5113,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -5091,20 +5134,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -5112,20 +5155,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -5133,20 +5176,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -5154,20 +5197,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5175,20 +5218,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5196,20 +5239,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5217,20 +5260,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5238,20 +5281,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5259,20 +5302,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5280,20 +5323,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5301,20 +5344,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5322,20 +5365,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5343,20 +5386,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5364,20 +5407,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5385,20 +5428,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5406,20 +5449,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5427,20 +5470,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5448,20 +5491,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5469,20 +5512,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5490,20 +5533,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5511,20 +5554,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5532,20 +5575,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5553,20 +5596,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5574,20 +5617,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5595,20 +5638,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5616,20 +5659,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5637,20 +5680,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5658,20 +5701,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5679,20 +5722,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5700,20 +5743,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5721,20 +5764,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5742,20 +5785,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5763,20 +5806,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5784,20 +5827,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5805,20 +5848,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5826,20 +5869,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -5847,20 +5890,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -5868,20 +5911,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -5889,20 +5932,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -5910,20 +5953,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -5931,20 +5974,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -5952,20 +5995,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -5973,20 +6016,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -5994,20 +6037,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -6015,20 +6058,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -6036,20 +6079,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -6057,20 +6100,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -6078,20 +6121,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -6099,20 +6142,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -6120,20 +6163,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -6141,20 +6184,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -6162,20 +6205,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6183,20 +6226,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6204,20 +6247,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6225,20 +6268,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6246,20 +6289,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6267,20 +6310,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6288,20 +6331,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6309,20 +6352,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6330,20 +6373,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6351,20 +6394,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6372,20 +6415,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6393,20 +6436,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6414,20 +6457,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6435,20 +6478,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6456,20 +6499,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6477,20 +6520,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6498,20 +6541,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6519,20 +6562,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6540,20 +6583,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6561,20 +6604,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6582,20 +6625,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6603,20 +6646,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6624,20 +6667,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6645,20 +6688,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6666,20 +6709,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6687,20 +6730,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6708,20 +6751,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6729,20 +6772,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6750,20 +6793,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B144" s="9" t="inlineStr">
+      <c r="B145" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6771,20 +6814,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6792,20 +6835,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6813,20 +6856,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -6834,20 +6877,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -6855,20 +6898,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -6876,20 +6919,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -6897,20 +6940,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -6918,20 +6961,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -6939,20 +6982,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -6960,20 +7003,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -6981,20 +7024,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -7002,20 +7045,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -7023,20 +7066,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -7044,20 +7087,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -7065,20 +7108,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -7086,20 +7129,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -7107,20 +7150,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -7128,20 +7171,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -7149,20 +7192,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -7170,20 +7213,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7191,20 +7234,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7212,20 +7255,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7233,20 +7276,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7254,20 +7297,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7275,20 +7318,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7296,20 +7339,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7317,20 +7360,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7338,20 +7381,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7359,20 +7402,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7380,20 +7423,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7401,20 +7444,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7422,20 +7465,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7443,20 +7486,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7464,20 +7507,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7485,20 +7528,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7506,20 +7549,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7527,20 +7570,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7548,20 +7591,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7569,20 +7612,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7590,20 +7633,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7611,20 +7654,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7632,20 +7675,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7653,20 +7696,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7674,20 +7717,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7695,20 +7738,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7716,20 +7759,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7737,20 +7780,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7758,20 +7801,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7779,20 +7822,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7800,20 +7843,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7821,20 +7864,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -7842,20 +7885,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -7863,20 +7906,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
-      <c r="A197" t="inlineStr">
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -7884,20 +7927,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="60" customHeight="1">
-      <c r="A198" t="inlineStr">
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -7905,20 +7948,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="60" customHeight="1">
-      <c r="A199" t="inlineStr">
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B199" s="8" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -7926,20 +7969,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C199" s="1" t="inlineStr">
+      <c r="C200" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="60" customHeight="1">
-      <c r="A200" t="inlineStr">
+    <row r="201" ht="60" customHeight="1">
+      <c r="A201" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -7947,16 +7990,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C200" s="1" t="inlineStr">
+      <c r="C201" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="201">
-      <c r="B201" s="1" t="n"/>
-      <c r="C201" s="1" t="n"/>
     </row>
     <row r="202">
       <c r="B202" s="1" t="n"/>
@@ -7968,6 +8007,7 @@
     </row>
     <row r="204">
       <c r="B204" s="1" t="n"/>
+      <c r="C204" s="1" t="n"/>
     </row>
     <row r="205">
       <c r="B205" s="1" t="n"/>
@@ -8043,6 +8083,9 @@
     </row>
     <row r="229">
       <c r="B229" s="1" t="n"/>
+    </row>
+    <row r="230">
+      <c r="B230" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,10 +547,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>27/09/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 7
+1 5 3 8
+5 8 9 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>26/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 5
@@ -558,14 +573,21 @@
 4 8 9 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 7/217 (3.23%)
+▶ Direct: 7/4128 (0.17%)
+▶ Total Sets hit: 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -573,7 +595,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/221 (4.52%)
 ▶ Direct: 10/4230 (0.24%)
@@ -581,13 +603,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -595,7 +617,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -617,7 +639,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/220 (5.91%)
 ▶ Direct: 13/4176 (0.31%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -639,7 +661,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/220 (6.82%)
 ▶ Direct: 15/4176 (0.36%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -661,7 +683,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -683,7 +705,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -705,7 +727,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -727,7 +749,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -749,7 +771,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -771,7 +793,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -793,7 +815,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -815,7 +837,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -837,7 +859,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -859,7 +881,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -881,7 +903,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -903,7 +925,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -925,7 +947,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -947,7 +969,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -969,7 +991,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -991,7 +1013,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1013,7 +1035,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1035,7 +1057,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1057,7 +1079,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1079,7 +1101,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1101,7 +1123,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1123,7 +1145,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1145,7 +1167,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1255,7 +1277,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1277,7 +1299,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1299,7 +1321,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1321,7 +1343,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1343,7 +1365,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1365,7 +1387,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1387,7 +1409,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1409,7 +1431,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1431,7 +1453,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1453,7 +1475,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1475,7 +1497,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1497,7 +1519,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1519,7 +1541,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1541,7 +1563,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1563,7 +1585,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1585,7 +1607,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1607,7 +1629,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1629,7 +1651,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1651,7 +1673,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1673,7 +1695,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1695,7 +1717,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1827,7 +1849,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1849,7 +1871,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1871,7 +1893,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1893,7 +1915,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1915,7 +1937,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1937,7 +1959,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1959,7 +1981,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1981,7 +2003,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2003,7 +2025,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2025,7 +2047,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2047,7 +2069,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2069,7 +2091,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2091,7 +2113,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2113,7 +2135,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2135,7 +2157,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2157,7 +2179,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2179,7 +2201,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2201,7 +2223,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2223,7 +2245,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2245,7 +2267,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2267,7 +2289,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2289,7 +2311,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2311,7 +2333,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2333,7 +2355,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2355,7 +2377,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2377,7 +2399,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2399,7 +2421,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2421,7 +2443,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2443,7 +2465,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2465,7 +2487,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2487,7 +2509,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2509,7 +2531,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2531,7 +2553,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2553,7 +2575,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2575,7 +2597,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2597,7 +2619,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2619,7 +2641,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2641,7 +2663,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2663,7 +2685,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2685,7 +2707,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2707,7 +2729,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2729,7 +2751,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2751,7 +2773,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2773,7 +2795,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2795,7 +2817,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2817,7 +2839,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2839,7 +2861,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2861,7 +2883,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2883,7 +2905,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2905,7 +2927,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2927,7 +2949,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2949,7 +2971,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2971,7 +2993,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3103,7 +3125,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3125,7 +3147,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3147,7 +3169,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3169,7 +3191,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3191,7 +3213,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3213,7 +3235,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3235,7 +3257,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3257,7 +3279,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3279,7 +3301,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3301,7 +3323,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3323,7 +3345,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3345,7 +3367,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3367,7 +3389,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3389,7 +3411,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3411,7 +3433,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3433,7 +3455,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3477,7 +3499,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3499,7 +3521,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3521,7 +3543,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3543,7 +3565,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3565,7 +3587,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
+      <c r="B141" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3587,7 +3609,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B141" s="12" t="inlineStr">
+      <c r="B142" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3609,7 +3631,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B142" s="12" t="inlineStr">
+      <c r="B143" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3631,7 +3653,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3639,13 +3661,13 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B143" s="12" t="inlineStr">
+      <c r="B144" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3653,7 +3675,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3661,13 +3683,13 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B144" s="10" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3675,7 +3697,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3683,13 +3705,13 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="B146" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3697,7 +3719,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3705,13 +3727,13 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3719,7 +3741,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3727,13 +3749,13 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3741,7 +3763,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3749,17 +3771,17 @@
         </is>
       </c>
     </row>
-    <row r="148" customHeight="1">
-      <c r="B148" s="4" t="n"/>
-      <c r="C148" s="1" t="n"/>
-    </row>
     <row r="149" customHeight="1">
-      <c r="B149" s="1" t="n"/>
+      <c r="B149" s="4" t="n"/>
       <c r="C149" s="1" t="n"/>
     </row>
     <row r="150" customHeight="1">
       <c r="B150" s="1" t="n"/>
       <c r="C150" s="1" t="n"/>
+    </row>
+    <row r="151" customHeight="1">
+      <c r="B151" s="1" t="n"/>
+      <c r="C151" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3772,7 +3794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C230"/>
+  <dimension ref="A1:C231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3800,10 +3822,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>26/09/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>6 9 4 4
+1 1 9 7
+2 3 2 3
+5 7 0 8</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 13/4302 (0.30%)
+✅ iBet: 13/226 (5.75%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>1 8 7 4
 0 5 9 5
@@ -3811,20 +3854,20 @@
 9 4 8 7</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4128 (0.22%)
 ✅ iBet: 9/217 (4.15%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>9 4 2 7
 3 3 9 1
@@ -3832,20 +3875,20 @@
 7 6 5 2</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>3 9 6 1
 7 0 3 5
@@ -3853,20 +3896,20 @@
 4 2 1 4</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>6 7 1 1
 9 2 3 0
@@ -3874,20 +3917,20 @@
 0 6 2 5</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>1 0 7 7
 4 4 0 3
@@ -3895,20 +3938,20 @@
 8 5 3 2</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4176 (0.22%)
 ✅ iBet: 9/220 (4.09%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -3916,20 +3959,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -3937,20 +3980,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -3958,20 +4001,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -3979,20 +4022,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -4000,20 +4043,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -4021,20 +4064,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -4042,20 +4085,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -4063,20 +4106,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -4084,20 +4127,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -4105,20 +4148,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -4126,20 +4169,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -4147,20 +4190,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -4168,20 +4211,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -4189,20 +4232,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -4210,20 +4253,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4231,20 +4274,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4252,20 +4295,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4273,20 +4316,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4294,20 +4337,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4315,20 +4358,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4336,20 +4379,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4357,20 +4400,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4378,20 +4421,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4399,20 +4442,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4420,20 +4463,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4441,20 +4484,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4462,20 +4505,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4483,20 +4526,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4504,20 +4547,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4525,20 +4568,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4546,20 +4589,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4567,20 +4610,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4588,20 +4631,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4609,20 +4652,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4630,20 +4673,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4651,20 +4694,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4672,20 +4715,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4693,20 +4736,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4714,20 +4757,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4735,20 +4778,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4756,20 +4799,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4777,20 +4820,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4798,20 +4841,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4819,20 +4862,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4840,20 +4883,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4861,20 +4904,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4882,20 +4925,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -4903,20 +4946,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -4924,20 +4967,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -4945,20 +4988,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -4966,20 +5009,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -4987,20 +5030,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -5008,20 +5051,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -5029,20 +5072,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -5050,20 +5093,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -5071,20 +5114,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -5092,20 +5135,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -5113,20 +5156,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -5134,20 +5177,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -5155,20 +5198,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -5176,20 +5219,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -5197,20 +5240,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5218,20 +5261,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5239,20 +5282,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5260,20 +5303,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5281,20 +5324,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5302,20 +5345,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5323,20 +5366,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5344,20 +5387,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5365,20 +5408,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5386,20 +5429,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5407,20 +5450,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5428,20 +5471,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5449,20 +5492,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5470,20 +5513,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5491,20 +5534,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5512,20 +5555,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5533,20 +5576,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5554,20 +5597,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5575,20 +5618,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5596,20 +5639,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5617,20 +5660,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5638,20 +5681,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5659,20 +5702,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5680,20 +5723,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5701,20 +5744,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5722,20 +5765,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5743,20 +5786,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5764,20 +5807,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5785,20 +5828,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5806,20 +5849,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5827,20 +5870,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5848,20 +5891,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5869,20 +5912,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -5890,20 +5933,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -5911,20 +5954,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -5932,20 +5975,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -5953,20 +5996,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -5974,20 +6017,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -5995,20 +6038,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -6016,20 +6059,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -6037,20 +6080,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -6058,20 +6101,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -6079,20 +6122,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -6100,20 +6143,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -6121,20 +6164,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -6142,20 +6185,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -6163,20 +6206,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -6184,20 +6227,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -6205,20 +6248,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6226,20 +6269,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6247,20 +6290,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6268,20 +6311,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6289,20 +6332,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6310,20 +6353,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6331,20 +6374,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6352,20 +6395,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6373,20 +6416,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6394,20 +6437,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6415,20 +6458,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6436,20 +6479,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6457,20 +6500,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6478,20 +6521,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6499,20 +6542,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6520,20 +6563,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6541,20 +6584,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6562,20 +6605,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6583,20 +6626,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6604,20 +6647,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6625,20 +6668,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6646,20 +6689,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6667,20 +6710,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6688,20 +6731,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6709,20 +6752,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6730,20 +6773,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6751,20 +6794,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6772,20 +6815,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B144" s="11" t="inlineStr">
+      <c r="B145" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6793,20 +6836,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr">
+      <c r="B146" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6814,20 +6857,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6835,20 +6878,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6856,20 +6899,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -6877,20 +6920,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -6898,20 +6941,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -6919,20 +6962,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -6940,20 +6983,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -6961,20 +7004,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -6982,20 +7025,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -7003,20 +7046,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -7024,20 +7067,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -7045,20 +7088,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -7066,20 +7109,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -7087,20 +7130,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -7108,20 +7151,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -7129,20 +7172,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -7150,20 +7193,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -7171,20 +7214,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -7192,20 +7235,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -7213,20 +7256,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7234,20 +7277,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7255,20 +7298,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7276,20 +7319,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7297,20 +7340,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7318,20 +7361,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7339,20 +7382,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7360,20 +7403,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7381,20 +7424,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7402,20 +7445,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7423,20 +7466,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7444,20 +7487,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7465,20 +7508,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7486,20 +7529,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7507,20 +7550,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7528,20 +7571,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7549,20 +7592,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7570,20 +7613,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7591,20 +7634,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7612,20 +7655,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7633,20 +7676,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7654,20 +7697,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7675,20 +7718,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7696,20 +7739,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7717,20 +7760,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7738,20 +7781,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7759,20 +7802,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7780,20 +7823,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7801,20 +7844,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7822,20 +7865,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7843,20 +7886,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7864,20 +7907,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -7885,20 +7928,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
-      <c r="A197" t="inlineStr">
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -7906,20 +7949,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="60" customHeight="1">
-      <c r="A198" t="inlineStr">
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -7927,20 +7970,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="60" customHeight="1">
-      <c r="A199" t="inlineStr">
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B199" s="8" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -7948,20 +7991,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C199" s="1" t="inlineStr">
+      <c r="C200" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="60" customHeight="1">
-      <c r="A200" t="inlineStr">
+    <row r="201" ht="60" customHeight="1">
+      <c r="A201" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -7969,20 +8012,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C200" s="1" t="inlineStr">
+      <c r="C201" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="60" customHeight="1">
-      <c r="A201" t="inlineStr">
+    <row r="202" ht="60" customHeight="1">
+      <c r="A202" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B201" s="8" t="inlineStr">
+      <c r="B202" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -7990,16 +8033,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C201" s="1" t="inlineStr">
+      <c r="C202" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="202">
-      <c r="B202" s="1" t="n"/>
-      <c r="C202" s="1" t="n"/>
     </row>
     <row r="203">
       <c r="B203" s="1" t="n"/>
@@ -8011,6 +8050,7 @@
     </row>
     <row r="205">
       <c r="B205" s="1" t="n"/>
+      <c r="C205" s="1" t="n"/>
     </row>
     <row r="206">
       <c r="B206" s="1" t="n"/>
@@ -8086,6 +8126,9 @@
     </row>
     <row r="230">
       <c r="B230" s="1" t="n"/>
+    </row>
+    <row r="231">
+      <c r="B231" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27/09/2026 (Sun)</t>
+          <t>30/09/2026 (Wed)</t>
         </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
@@ -562,10 +562,32 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>27/09/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 7
+1 5 3 8
+5 8 9 0</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 12/221 (5.43%)
+▶ Direct: 12/4230 (0.28%)
+▶ Total Sets hit: 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>26/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 5
@@ -573,7 +595,7 @@
 4 8 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -581,13 +603,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -595,7 +617,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/221 (4.52%)
 ▶ Direct: 10/4230 (0.24%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -617,7 +639,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -639,7 +661,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/220 (5.91%)
 ▶ Direct: 13/4176 (0.31%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -661,7 +683,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/220 (6.82%)
 ▶ Direct: 15/4176 (0.36%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -683,7 +705,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -705,7 +727,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -727,7 +749,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -749,7 +771,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -771,7 +793,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -793,7 +815,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -815,7 +837,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -837,7 +859,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -859,7 +881,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -881,7 +903,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -903,7 +925,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -925,7 +947,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -947,7 +969,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -969,7 +991,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -991,7 +1013,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1013,7 +1035,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1035,7 +1057,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1057,7 +1079,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1079,7 +1101,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1101,7 +1123,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1123,7 +1145,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1145,7 +1167,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1255,7 +1277,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1277,7 +1299,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1299,7 +1321,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1321,7 +1343,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1343,7 +1365,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1365,7 +1387,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1387,7 +1409,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1409,7 +1431,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1431,7 +1453,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1453,7 +1475,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1475,7 +1497,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1497,7 +1519,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1519,7 +1541,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1541,7 +1563,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1563,7 +1585,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1585,7 +1607,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1607,7 +1629,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1629,7 +1651,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1651,7 +1673,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1673,7 +1695,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1695,7 +1717,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1827,7 +1849,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1849,7 +1871,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1871,7 +1893,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1893,7 +1915,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1915,7 +1937,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1937,7 +1959,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1959,7 +1981,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1981,7 +2003,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2003,7 +2025,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2025,7 +2047,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2047,7 +2069,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2069,7 +2091,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2091,7 +2113,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2113,7 +2135,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2135,7 +2157,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2157,7 +2179,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2179,7 +2201,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2201,7 +2223,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2223,7 +2245,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2245,7 +2267,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2267,7 +2289,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2289,7 +2311,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2311,7 +2333,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2333,7 +2355,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2355,7 +2377,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2377,7 +2399,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2399,7 +2421,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2421,7 +2443,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2443,7 +2465,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2465,7 +2487,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2487,7 +2509,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2509,7 +2531,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2531,7 +2553,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2553,7 +2575,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2575,7 +2597,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2597,7 +2619,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2619,7 +2641,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2641,7 +2663,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2663,7 +2685,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2685,7 +2707,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2707,7 +2729,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2729,7 +2751,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2751,7 +2773,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2773,7 +2795,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2795,7 +2817,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2817,7 +2839,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2839,7 +2861,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2861,7 +2883,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2883,7 +2905,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2905,7 +2927,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2927,7 +2949,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2949,7 +2971,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2971,7 +2993,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3103,7 +3125,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3125,7 +3147,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3147,7 +3169,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3169,7 +3191,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3191,7 +3213,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3213,7 +3235,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3235,7 +3257,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3257,7 +3279,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3279,7 +3301,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3301,7 +3323,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3323,7 +3345,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3345,7 +3367,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3367,7 +3389,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3389,7 +3411,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3411,7 +3433,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3433,7 +3455,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3477,7 +3499,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3499,7 +3521,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3521,7 +3543,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3543,7 +3565,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3565,7 +3587,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
+      <c r="B141" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3587,7 +3609,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B141" s="12" t="inlineStr">
+      <c r="B142" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3609,7 +3631,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B142" s="12" t="inlineStr">
+      <c r="B143" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3631,7 +3653,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3639,13 +3661,13 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B143" s="12" t="inlineStr">
+      <c r="B144" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3653,7 +3675,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3661,13 +3683,13 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B144" s="12" t="inlineStr">
+      <c r="B145" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3675,7 +3697,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3683,13 +3705,13 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B145" s="10" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3697,7 +3719,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3705,13 +3727,13 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B146" s="7" t="inlineStr">
+      <c r="B147" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3719,7 +3741,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3727,13 +3749,13 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B148" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3741,7 +3763,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3749,13 +3771,13 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3763,7 +3785,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3771,17 +3793,17 @@
         </is>
       </c>
     </row>
-    <row r="149" customHeight="1">
-      <c r="B149" s="4" t="n"/>
-      <c r="C149" s="1" t="n"/>
-    </row>
     <row r="150" customHeight="1">
-      <c r="B150" s="1" t="n"/>
+      <c r="B150" s="4" t="n"/>
       <c r="C150" s="1" t="n"/>
     </row>
     <row r="151" customHeight="1">
       <c r="B151" s="1" t="n"/>
       <c r="C151" s="1" t="n"/>
+    </row>
+    <row r="152" customHeight="1">
+      <c r="B152" s="1" t="n"/>
+      <c r="C152" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3794,7 +3816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C231"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3822,10 +3844,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>27/09/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>6 7 8 8
+1 3 7 2
+3 5 6 1
+4 9 0 0</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 11/4302 (0.26%)
+✅ iBet: 11/226 (4.87%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>26/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>6 9 4 4
 1 1 9 7
@@ -3833,20 +3876,20 @@
 5 7 0 8</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>1 8 7 4
 0 5 9 5
@@ -3854,20 +3897,20 @@
 9 4 8 7</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4128 (0.22%)
 ✅ iBet: 9/217 (4.15%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>9 4 2 7
 3 3 9 1
@@ -3875,20 +3918,20 @@
 7 6 5 2</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>3 9 6 1
 7 0 3 5
@@ -3896,20 +3939,20 @@
 4 2 1 4</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>6 7 1 1
 9 2 3 0
@@ -3917,20 +3960,20 @@
 0 6 2 5</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>1 0 7 7
 4 4 0 3
@@ -3938,20 +3981,20 @@
 8 5 3 2</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4176 (0.22%)
 ✅ iBet: 9/220 (4.09%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -3959,20 +4002,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -3980,20 +4023,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -4001,20 +4044,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -4022,20 +4065,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -4043,20 +4086,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -4064,20 +4107,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -4085,20 +4128,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -4106,20 +4149,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -4127,20 +4170,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -4148,20 +4191,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -4169,20 +4212,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -4190,20 +4233,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -4211,20 +4254,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -4232,20 +4275,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -4253,20 +4296,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4274,20 +4317,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4295,20 +4338,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4316,20 +4359,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4337,20 +4380,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4358,20 +4401,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4379,20 +4422,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4400,20 +4443,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4421,20 +4464,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4442,20 +4485,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4463,20 +4506,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4484,20 +4527,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4505,20 +4548,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4526,20 +4569,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4547,20 +4590,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4568,20 +4611,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4589,20 +4632,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4610,20 +4653,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4631,20 +4674,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4652,20 +4695,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4673,20 +4716,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4694,20 +4737,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4715,20 +4758,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4736,20 +4779,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4757,20 +4800,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4778,20 +4821,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4799,20 +4842,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4820,20 +4863,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4841,20 +4884,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4862,20 +4905,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4883,20 +4926,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4904,20 +4947,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4925,20 +4968,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -4946,20 +4989,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -4967,20 +5010,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -4988,20 +5031,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -5009,20 +5052,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -5030,20 +5073,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -5051,20 +5094,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -5072,20 +5115,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -5093,20 +5136,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -5114,20 +5157,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -5135,20 +5178,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -5156,20 +5199,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -5177,20 +5220,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -5198,20 +5241,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -5219,20 +5262,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -5240,20 +5283,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5261,20 +5304,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5282,20 +5325,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5303,20 +5346,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5324,20 +5367,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5345,20 +5388,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5366,20 +5409,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5387,20 +5430,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5408,20 +5451,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5429,20 +5472,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5450,20 +5493,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5471,20 +5514,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5492,20 +5535,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5513,20 +5556,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5534,20 +5577,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5555,20 +5598,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5576,20 +5619,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5597,20 +5640,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5618,20 +5661,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5639,20 +5682,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5660,20 +5703,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5681,20 +5724,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5702,20 +5745,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5723,20 +5766,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5744,20 +5787,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5765,20 +5808,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5786,20 +5829,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5807,20 +5850,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5828,20 +5871,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5849,20 +5892,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5870,20 +5913,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5891,20 +5934,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5912,20 +5955,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -5933,20 +5976,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -5954,20 +5997,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -5975,20 +6018,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -5996,20 +6039,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -6017,20 +6060,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -6038,20 +6081,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -6059,20 +6102,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -6080,20 +6123,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -6101,20 +6144,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -6122,20 +6165,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -6143,20 +6186,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -6164,20 +6207,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -6185,20 +6228,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -6206,20 +6249,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -6227,20 +6270,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -6248,20 +6291,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6269,20 +6312,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6290,20 +6333,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6311,20 +6354,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6332,20 +6375,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6353,20 +6396,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6374,20 +6417,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6395,20 +6438,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6416,20 +6459,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6437,20 +6480,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6458,20 +6501,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6479,20 +6522,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6500,20 +6543,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6521,20 +6564,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6542,20 +6585,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6563,20 +6606,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6584,20 +6627,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6605,20 +6648,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6626,20 +6669,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6647,20 +6690,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6668,20 +6711,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6689,20 +6732,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6710,20 +6753,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6731,20 +6774,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6752,20 +6795,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6773,20 +6816,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6794,20 +6837,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B144" s="11" t="inlineStr">
+      <c r="B145" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6815,20 +6858,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B145" s="11" t="inlineStr">
+      <c r="B146" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6836,20 +6879,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B146" s="9" t="inlineStr">
+      <c r="B147" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6857,20 +6900,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6878,20 +6921,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6899,20 +6942,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -6920,20 +6963,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -6941,20 +6984,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -6962,20 +7005,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -6983,20 +7026,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -7004,20 +7047,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -7025,20 +7068,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -7046,20 +7089,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -7067,20 +7110,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -7088,20 +7131,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -7109,20 +7152,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -7130,20 +7173,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -7151,20 +7194,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -7172,20 +7215,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -7193,20 +7236,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -7214,20 +7257,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -7235,20 +7278,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -7256,20 +7299,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7277,20 +7320,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7298,20 +7341,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7319,20 +7362,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7340,20 +7383,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7361,20 +7404,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7382,20 +7425,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7403,20 +7446,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7424,20 +7467,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7445,20 +7488,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7466,20 +7509,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7487,20 +7530,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7508,20 +7551,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7529,20 +7572,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7550,20 +7593,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7571,20 +7614,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7592,20 +7635,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7613,20 +7656,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7634,20 +7677,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7655,20 +7698,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7676,20 +7719,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7697,20 +7740,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7718,20 +7761,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7739,20 +7782,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7760,20 +7803,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7781,20 +7824,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7802,20 +7845,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7823,20 +7866,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7844,20 +7887,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7865,20 +7908,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7886,20 +7929,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7907,20 +7950,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
-      <c r="A197" t="inlineStr">
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -7928,20 +7971,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="60" customHeight="1">
-      <c r="A198" t="inlineStr">
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -7949,20 +7992,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="60" customHeight="1">
-      <c r="A199" t="inlineStr">
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B199" s="8" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -7970,20 +8013,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C199" s="1" t="inlineStr">
+      <c r="C200" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="60" customHeight="1">
-      <c r="A200" t="inlineStr">
+    <row r="201" ht="60" customHeight="1">
+      <c r="A201" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -7991,20 +8034,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C200" s="1" t="inlineStr">
+      <c r="C201" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="60" customHeight="1">
-      <c r="A201" t="inlineStr">
+    <row r="202" ht="60" customHeight="1">
+      <c r="A202" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B201" s="8" t="inlineStr">
+      <c r="B202" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -8012,20 +8055,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C201" s="1" t="inlineStr">
+      <c r="C202" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="60" customHeight="1">
-      <c r="A202" t="inlineStr">
+    <row r="203" ht="60" customHeight="1">
+      <c r="A203" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B202" s="8" t="inlineStr">
+      <c r="B203" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -8033,16 +8076,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C202" s="1" t="inlineStr">
+      <c r="C203" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="203">
-      <c r="B203" s="1" t="n"/>
-      <c r="C203" s="1" t="n"/>
     </row>
     <row r="204">
       <c r="B204" s="1" t="n"/>
@@ -8054,6 +8093,7 @@
     </row>
     <row r="206">
       <c r="B206" s="1" t="n"/>
+      <c r="C206" s="1" t="n"/>
     </row>
     <row r="207">
       <c r="B207" s="1" t="n"/>
@@ -8129,6 +8169,9 @@
     </row>
     <row r="231">
       <c r="B231" s="1" t="n"/>
+    </row>
+    <row r="232">
+      <c r="B232" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30/09/2026 (Wed)</t>
+          <t>03/10/2026 (Sat)</t>
         </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
@@ -562,7 +562,7 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27/09/2026 (Sun)</t>
+          <t>30/09/2026 (Wed)</t>
         </is>
       </c>
       <c r="B3" s="18" t="inlineStr">
@@ -575,19 +575,41 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>▶ iBet: 2/221 (0.90%)
+▶ Direct: 2/4230 (0.05%)
+▶ Total Sets hit: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>27/09/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 7
+1 5 3 8
+5 8 9 0</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
 ▶ Total Sets hit: 12</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>26/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 5
@@ -595,7 +617,7 @@
 4 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -617,7 +639,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/221 (4.52%)
 ▶ Direct: 10/4230 (0.24%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -639,7 +661,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -661,7 +683,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/220 (5.91%)
 ▶ Direct: 13/4176 (0.31%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -683,7 +705,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/220 (6.82%)
 ▶ Direct: 15/4176 (0.36%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -705,7 +727,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -727,7 +749,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -749,7 +771,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -771,7 +793,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -793,7 +815,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -815,7 +837,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -837,7 +859,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -859,7 +881,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -881,7 +903,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -903,7 +925,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -925,7 +947,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -947,7 +969,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -969,7 +991,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -991,7 +1013,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1013,7 +1035,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1035,7 +1057,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1057,7 +1079,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1079,7 +1101,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1101,7 +1123,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1123,7 +1145,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1145,7 +1167,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1255,7 +1277,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1277,7 +1299,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1299,7 +1321,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1321,7 +1343,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1343,7 +1365,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1365,7 +1387,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1387,7 +1409,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1409,7 +1431,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1431,7 +1453,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1453,7 +1475,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1475,7 +1497,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1497,7 +1519,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1519,7 +1541,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1541,7 +1563,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1563,7 +1585,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1585,7 +1607,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1607,7 +1629,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1629,7 +1651,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1651,7 +1673,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1673,7 +1695,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1695,7 +1717,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1827,7 +1849,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1849,7 +1871,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1871,7 +1893,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1893,7 +1915,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1915,7 +1937,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1937,7 +1959,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="14" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1959,7 +1981,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1981,7 +2003,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2003,7 +2025,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2025,7 +2047,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2047,7 +2069,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2069,7 +2091,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2091,7 +2113,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2113,7 +2135,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2135,7 +2157,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2157,7 +2179,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2179,7 +2201,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2201,7 +2223,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2223,7 +2245,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2245,7 +2267,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2267,7 +2289,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2289,7 +2311,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2311,7 +2333,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2333,7 +2355,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2355,7 +2377,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2377,7 +2399,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2399,7 +2421,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2421,7 +2443,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2443,7 +2465,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2465,7 +2487,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2487,7 +2509,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2509,7 +2531,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2531,7 +2553,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2553,7 +2575,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2575,7 +2597,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2597,7 +2619,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2619,7 +2641,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2641,7 +2663,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2663,7 +2685,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2685,7 +2707,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2707,7 +2729,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2729,7 +2751,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2751,7 +2773,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2773,7 +2795,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2795,7 +2817,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2817,7 +2839,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2839,7 +2861,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2861,7 +2883,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2883,7 +2905,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2905,7 +2927,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2927,7 +2949,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2949,7 +2971,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2971,7 +2993,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3103,7 +3125,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3125,7 +3147,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3147,7 +3169,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3169,7 +3191,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3191,7 +3213,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3213,7 +3235,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3235,7 +3257,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3257,7 +3279,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3279,7 +3301,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3301,7 +3323,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3323,7 +3345,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3345,7 +3367,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3367,7 +3389,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3389,7 +3411,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3411,7 +3433,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3433,7 +3455,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3477,7 +3499,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3499,7 +3521,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3521,7 +3543,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3543,7 +3565,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3565,7 +3587,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
+      <c r="B141" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3587,7 +3609,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B141" s="12" t="inlineStr">
+      <c r="B142" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3609,7 +3631,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B142" s="12" t="inlineStr">
+      <c r="B143" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3631,7 +3653,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3639,13 +3661,13 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B143" s="12" t="inlineStr">
+      <c r="B144" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3653,7 +3675,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3661,13 +3683,13 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B144" s="12" t="inlineStr">
+      <c r="B145" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3675,7 +3697,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3683,13 +3705,13 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B145" s="12" t="inlineStr">
+      <c r="B146" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3697,7 +3719,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3705,13 +3727,13 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B146" s="10" t="inlineStr">
+      <c r="B147" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3719,7 +3741,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3727,13 +3749,13 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B148" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3741,7 +3763,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3749,13 +3771,13 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3763,7 +3785,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3771,13 +3793,13 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3785,7 +3807,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3793,17 +3815,17 @@
         </is>
       </c>
     </row>
-    <row r="150" customHeight="1">
-      <c r="B150" s="4" t="n"/>
-      <c r="C150" s="1" t="n"/>
-    </row>
     <row r="151" customHeight="1">
-      <c r="B151" s="1" t="n"/>
+      <c r="B151" s="4" t="n"/>
       <c r="C151" s="1" t="n"/>
     </row>
     <row r="152" customHeight="1">
       <c r="B152" s="1" t="n"/>
       <c r="C152" s="1" t="n"/>
+    </row>
+    <row r="153" customHeight="1">
+      <c r="B153" s="1" t="n"/>
+      <c r="C153" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3816,7 +3838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C232"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3844,10 +3866,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30/09/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>3 0 2 5
+9 2 0 4
+8 7 6 3
+4 8 7 1</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 11/3672 (0.30%)
+✅ iBet: 11/195 (5.64%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>27/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>6 7 8 8
 1 3 7 2
@@ -3855,20 +3898,20 @@
 4 9 0 0</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>26/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>6 9 4 4
 1 1 9 7
@@ -3876,20 +3919,20 @@
 5 7 0 8</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>1 8 7 4
 0 5 9 5
@@ -3897,20 +3940,20 @@
 9 4 8 7</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4128 (0.22%)
 ✅ iBet: 9/217 (4.15%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>9 4 2 7
 3 3 9 1
@@ -3918,20 +3961,20 @@
 7 6 5 2</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>3 9 6 1
 7 0 3 5
@@ -3939,20 +3982,20 @@
 4 2 1 4</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>6 7 1 1
 9 2 3 0
@@ -3960,20 +4003,20 @@
 0 6 2 5</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>1 0 7 7
 4 4 0 3
@@ -3981,20 +4024,20 @@
 8 5 3 2</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4176 (0.22%)
 ✅ iBet: 9/220 (4.09%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -4002,20 +4045,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -4023,20 +4066,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -4044,20 +4087,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -4065,20 +4108,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -4086,20 +4129,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -4107,20 +4150,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -4128,20 +4171,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -4149,20 +4192,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -4170,20 +4213,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -4191,20 +4234,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -4212,20 +4255,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -4233,20 +4276,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -4254,20 +4297,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -4275,20 +4318,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -4296,20 +4339,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4317,20 +4360,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4338,20 +4381,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4359,20 +4402,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4380,20 +4423,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4401,20 +4444,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4422,20 +4465,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4443,20 +4486,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4464,20 +4507,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4485,20 +4528,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4506,20 +4549,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4527,20 +4570,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4548,20 +4591,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4569,20 +4612,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4590,20 +4633,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4611,20 +4654,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4632,20 +4675,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4653,20 +4696,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4674,20 +4717,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4695,20 +4738,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4716,20 +4759,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4737,20 +4780,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4758,20 +4801,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4779,20 +4822,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4800,20 +4843,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4821,20 +4864,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4842,20 +4885,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4863,20 +4906,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4884,20 +4927,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4905,20 +4948,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4926,20 +4969,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4947,20 +4990,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4968,20 +5011,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -4989,20 +5032,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -5010,20 +5053,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -5031,20 +5074,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -5052,20 +5095,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -5073,20 +5116,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -5094,20 +5137,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -5115,20 +5158,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -5136,20 +5179,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -5157,20 +5200,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -5178,20 +5221,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -5199,20 +5242,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -5220,20 +5263,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -5241,20 +5284,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -5262,20 +5305,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -5283,20 +5326,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5304,20 +5347,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5325,20 +5368,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5346,20 +5389,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5367,20 +5410,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5388,20 +5431,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5409,20 +5452,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5430,20 +5473,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5451,20 +5494,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5472,20 +5515,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5493,20 +5536,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5514,20 +5557,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5535,20 +5578,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5556,20 +5599,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5577,20 +5620,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5598,20 +5641,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5619,20 +5662,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5640,20 +5683,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5661,20 +5704,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5682,20 +5725,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5703,20 +5746,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5724,20 +5767,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5745,20 +5788,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5766,20 +5809,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5787,20 +5830,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5808,20 +5851,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5829,20 +5872,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5850,20 +5893,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5871,20 +5914,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5892,20 +5935,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5913,20 +5956,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5934,20 +5977,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5955,20 +5998,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -5976,20 +6019,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -5997,20 +6040,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -6018,20 +6061,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -6039,20 +6082,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -6060,20 +6103,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -6081,20 +6124,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -6102,20 +6145,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -6123,20 +6166,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -6144,20 +6187,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -6165,20 +6208,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -6186,20 +6229,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -6207,20 +6250,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -6228,20 +6271,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -6249,20 +6292,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -6270,20 +6313,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -6291,20 +6334,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6312,20 +6355,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6333,20 +6376,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6354,20 +6397,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6375,20 +6418,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6396,20 +6439,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6417,20 +6460,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6438,20 +6481,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6459,20 +6502,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6480,20 +6523,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6501,20 +6544,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6522,20 +6565,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6543,20 +6586,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6564,20 +6607,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6585,20 +6628,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6606,20 +6649,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6627,20 +6670,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6648,20 +6691,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6669,20 +6712,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6690,20 +6733,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6711,20 +6754,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6732,20 +6775,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6753,20 +6796,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6774,20 +6817,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6795,20 +6838,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6816,20 +6859,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B144" s="11" t="inlineStr">
+      <c r="B145" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6837,20 +6880,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B145" s="11" t="inlineStr">
+      <c r="B146" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6858,20 +6901,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B146" s="11" t="inlineStr">
+      <c r="B147" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6879,20 +6922,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr">
+      <c r="B148" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6900,20 +6943,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6921,20 +6964,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6942,20 +6985,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -6963,20 +7006,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -6984,20 +7027,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -7005,20 +7048,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -7026,20 +7069,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -7047,20 +7090,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -7068,20 +7111,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -7089,20 +7132,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -7110,20 +7153,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -7131,20 +7174,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -7152,20 +7195,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -7173,20 +7216,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -7194,20 +7237,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -7215,20 +7258,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -7236,20 +7279,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -7257,20 +7300,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -7278,20 +7321,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -7299,20 +7342,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7320,20 +7363,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7341,20 +7384,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7362,20 +7405,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7383,20 +7426,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7404,20 +7447,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7425,20 +7468,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7446,20 +7489,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7467,20 +7510,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7488,20 +7531,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7509,20 +7552,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7530,20 +7573,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7551,20 +7594,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7572,20 +7615,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7593,20 +7636,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7614,20 +7657,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7635,20 +7678,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7656,20 +7699,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7677,20 +7720,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7698,20 +7741,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7719,20 +7762,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7740,20 +7783,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7761,20 +7804,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7782,20 +7825,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7803,20 +7846,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7824,20 +7867,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7845,20 +7888,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7866,20 +7909,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7887,20 +7930,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7908,20 +7951,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7929,20 +7972,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
-      <c r="A197" t="inlineStr">
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7950,20 +7993,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="60" customHeight="1">
-      <c r="A198" t="inlineStr">
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -7971,20 +8014,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="60" customHeight="1">
-      <c r="A199" t="inlineStr">
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B199" s="8" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -7992,20 +8035,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C199" s="1" t="inlineStr">
+      <c r="C200" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="60" customHeight="1">
-      <c r="A200" t="inlineStr">
+    <row r="201" ht="60" customHeight="1">
+      <c r="A201" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -8013,20 +8056,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C200" s="1" t="inlineStr">
+      <c r="C201" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="60" customHeight="1">
-      <c r="A201" t="inlineStr">
+    <row r="202" ht="60" customHeight="1">
+      <c r="A202" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B201" s="8" t="inlineStr">
+      <c r="B202" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -8034,20 +8077,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C201" s="1" t="inlineStr">
+      <c r="C202" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="60" customHeight="1">
-      <c r="A202" t="inlineStr">
+    <row r="203" ht="60" customHeight="1">
+      <c r="A203" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B202" s="8" t="inlineStr">
+      <c r="B203" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -8055,20 +8098,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C202" s="1" t="inlineStr">
+      <c r="C203" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="60" customHeight="1">
-      <c r="A203" t="inlineStr">
+    <row r="204" ht="60" customHeight="1">
+      <c r="A204" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B203" s="8" t="inlineStr">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -8076,16 +8119,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C203" s="1" t="inlineStr">
+      <c r="C204" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="204">
-      <c r="B204" s="1" t="n"/>
-      <c r="C204" s="1" t="n"/>
     </row>
     <row r="205">
       <c r="B205" s="1" t="n"/>
@@ -8097,6 +8136,7 @@
     </row>
     <row r="207">
       <c r="B207" s="1" t="n"/>
+      <c r="C207" s="1" t="n"/>
     </row>
     <row r="208">
       <c r="B208" s="1" t="n"/>
@@ -8172,6 +8212,9 @@
     </row>
     <row r="232">
       <c r="B232" s="1" t="n"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,10 +547,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>04/10/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 8
+1 5 3 9
+5 8 9 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>03/10/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -558,14 +573,21 @@
 5 8 9 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 9/221 (4.07%)
+▶ Direct: 10/4230 (0.24%)
+▶ Total Sets hit: 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>30/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -573,7 +595,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 2/221 (0.90%)
 ▶ Direct: 2/4230 (0.05%)
@@ -581,13 +603,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>27/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -595,7 +617,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>26/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 5
@@ -617,7 +639,7 @@
 4 8 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -639,7 +661,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/221 (4.52%)
 ▶ Direct: 10/4230 (0.24%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -661,7 +683,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -683,7 +705,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/220 (5.91%)
 ▶ Direct: 13/4176 (0.31%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -705,7 +727,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/220 (6.82%)
 ▶ Direct: 15/4176 (0.36%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -727,7 +749,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -749,7 +771,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -771,7 +793,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -793,7 +815,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -815,7 +837,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -837,7 +859,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -859,7 +881,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -881,7 +903,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -903,7 +925,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -925,7 +947,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -947,7 +969,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -969,7 +991,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -991,7 +1013,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1013,7 +1035,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1035,7 +1057,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1057,7 +1079,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1079,7 +1101,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1101,7 +1123,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1123,7 +1145,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1145,7 +1167,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1167,7 +1189,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1211,7 +1233,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1255,7 +1277,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1277,7 +1299,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1299,7 +1321,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1321,7 +1343,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1343,7 +1365,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1365,7 +1387,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1387,7 +1409,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1409,7 +1431,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1431,7 +1453,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1453,7 +1475,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1475,7 +1497,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1497,7 +1519,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1519,7 +1541,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1541,7 +1563,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1563,7 +1585,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1585,7 +1607,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1607,7 +1629,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1629,7 +1651,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1651,7 +1673,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1673,7 +1695,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1695,7 +1717,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1717,7 +1739,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1827,7 +1849,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1849,7 +1871,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1871,7 +1893,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1893,7 +1915,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1915,7 +1937,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1937,7 +1959,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="14" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1959,7 +1981,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -1981,7 +2003,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2003,7 +2025,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2025,7 +2047,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2033,13 +2055,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2047,7 +2069,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -2055,13 +2077,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2069,7 +2091,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2077,13 +2099,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2091,7 +2113,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -2099,13 +2121,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2113,7 +2135,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -2121,13 +2143,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2135,7 +2157,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -2143,13 +2165,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2157,7 +2179,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -2165,13 +2187,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2179,7 +2201,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -2187,13 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -2201,7 +2223,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -2209,13 +2231,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -2223,7 +2245,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2231,13 +2253,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -2245,7 +2267,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -2253,13 +2275,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -2267,7 +2289,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -2275,13 +2297,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2289,7 +2311,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -2297,13 +2319,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -2311,7 +2333,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2319,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2333,7 +2355,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2341,13 +2363,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2355,7 +2377,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2363,13 +2385,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2377,7 +2399,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -2385,13 +2407,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2399,7 +2421,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -2407,13 +2429,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -2421,7 +2443,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -2429,13 +2451,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -2443,7 +2465,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2451,13 +2473,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -2465,7 +2487,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2473,13 +2495,13 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2487,7 +2509,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2495,13 +2517,13 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2509,7 +2531,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2517,13 +2539,13 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -2531,7 +2553,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2539,13 +2561,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2553,7 +2575,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -2561,13 +2583,13 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -2575,7 +2597,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2583,13 +2605,13 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2597,7 +2619,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2605,13 +2627,13 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -2619,7 +2641,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2627,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -2641,7 +2663,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2649,13 +2671,13 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -2663,7 +2685,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -2671,13 +2693,13 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -2685,7 +2707,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2693,13 +2715,13 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -2707,7 +2729,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -2715,13 +2737,13 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -2729,7 +2751,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -2737,13 +2759,13 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -2751,7 +2773,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -2759,13 +2781,13 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -2773,7 +2795,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2781,13 +2803,13 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -2795,7 +2817,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2803,13 +2825,13 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -2817,7 +2839,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -2825,13 +2847,13 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -2839,7 +2861,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -2847,13 +2869,13 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -2861,7 +2883,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2869,13 +2891,13 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -2883,7 +2905,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -2891,13 +2913,13 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -2905,7 +2927,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -2913,13 +2935,13 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2927,7 +2949,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2935,13 +2957,13 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -2949,7 +2971,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2957,13 +2979,13 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -2971,7 +2993,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2979,13 +3001,13 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -2993,7 +3015,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -3001,13 +3023,13 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -3015,7 +3037,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -3023,13 +3045,13 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3037,7 +3059,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -3045,13 +3067,13 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3059,7 +3081,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -3067,13 +3089,13 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B118" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3081,7 +3103,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3089,13 +3111,13 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3103,7 +3125,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3111,13 +3133,13 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B120" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -3125,7 +3147,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3133,13 +3155,13 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B120" s="12" t="inlineStr">
+      <c r="B121" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3147,7 +3169,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -3155,13 +3177,13 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B121" s="12" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -3169,7 +3191,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -3177,13 +3199,13 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B123" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -3191,7 +3213,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3199,13 +3221,13 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3213,7 +3235,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3221,13 +3243,13 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3235,7 +3257,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -3243,13 +3265,13 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B125" s="12" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -3257,7 +3279,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3265,13 +3287,13 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -3279,7 +3301,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3287,13 +3309,13 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B128" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3301,7 +3323,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3309,13 +3331,13 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B128" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -3323,7 +3345,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -3331,13 +3353,13 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3345,7 +3367,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -3353,13 +3375,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3367,7 +3389,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3375,13 +3397,13 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -3389,7 +3411,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -3397,13 +3419,13 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B133" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3411,7 +3433,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -3419,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -3433,7 +3455,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3441,13 +3463,13 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B134" s="12" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3455,7 +3477,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -3463,13 +3485,13 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3477,7 +3499,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -3485,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -3499,7 +3521,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -3507,13 +3529,13 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B138" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3521,7 +3543,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -3529,13 +3551,13 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -3543,7 +3565,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -3551,13 +3573,13 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -3565,7 +3587,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3573,13 +3595,13 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
+      <c r="B141" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3587,7 +3609,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3595,13 +3617,13 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B141" s="12" t="inlineStr">
+      <c r="B142" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -3609,7 +3631,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -3617,13 +3639,13 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B142" s="12" t="inlineStr">
+      <c r="B143" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -3631,7 +3653,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3639,13 +3661,13 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B143" s="12" t="inlineStr">
+      <c r="B144" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3653,7 +3675,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3661,13 +3683,13 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B144" s="12" t="inlineStr">
+      <c r="B145" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3675,7 +3697,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -3683,13 +3705,13 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B145" s="12" t="inlineStr">
+      <c r="B146" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3697,7 +3719,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3705,13 +3727,13 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B146" s="12" t="inlineStr">
+      <c r="B147" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -3719,7 +3741,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -3727,13 +3749,13 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B147" s="10" t="inlineStr">
+      <c r="B148" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3741,7 +3763,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -3749,13 +3771,13 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B149" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -3763,7 +3785,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -3771,13 +3793,13 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -3785,7 +3807,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -3793,13 +3815,13 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B150" s="6" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -3807,7 +3829,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -3815,17 +3837,17 @@
         </is>
       </c>
     </row>
-    <row r="151" customHeight="1">
-      <c r="B151" s="4" t="n"/>
-      <c r="C151" s="1" t="n"/>
-    </row>
     <row r="152" customHeight="1">
-      <c r="B152" s="1" t="n"/>
+      <c r="B152" s="4" t="n"/>
       <c r="C152" s="1" t="n"/>
     </row>
     <row r="153" customHeight="1">
       <c r="B153" s="1" t="n"/>
       <c r="C153" s="1" t="n"/>
+    </row>
+    <row r="154" customHeight="1">
+      <c r="B154" s="1" t="n"/>
+      <c r="C154" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3838,7 +3860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C233"/>
+  <dimension ref="A1:C234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3866,10 +3888,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03/10/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>0 8 2 9
+1 6 0 8
+5 7 3 1
+2 5 4 3</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 11/4302 (0.26%)
+✅ iBet: 11/226 (4.87%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>30/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>3 0 2 5
 9 2 0 4
@@ -3877,20 +3920,20 @@
 4 8 7 1</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>27/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>6 7 8 8
 1 3 7 2
@@ -3898,20 +3941,20 @@
 4 9 0 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>26/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>6 9 4 4
 1 1 9 7
@@ -3919,20 +3962,20 @@
 5 7 0 8</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>1 8 7 4
 0 5 9 5
@@ -3940,20 +3983,20 @@
 9 4 8 7</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4128 (0.22%)
 ✅ iBet: 9/217 (4.15%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>9 4 2 7
 3 3 9 1
@@ -3961,20 +4004,20 @@
 7 6 5 2</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>3 9 6 1
 7 0 3 5
@@ -3982,20 +4025,20 @@
 4 2 1 4</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>6 7 1 1
 9 2 3 0
@@ -4003,20 +4046,20 @@
 0 6 2 5</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>1 0 7 7
 4 4 0 3
@@ -4024,20 +4067,20 @@
 8 5 3 2</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4176 (0.22%)
 ✅ iBet: 9/220 (4.09%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>9 4 8 4
 6 1 9 0
@@ -4045,20 +4088,20 @@
 0 5 7 3</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>0 6 2 0
 3 9 5 4
@@ -4066,20 +4109,20 @@
 4 8 6 3</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>0 7 7 0
 1 5 2 4
@@ -4087,20 +4130,20 @@
 9 1 6 5</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>1 2 5 3
 9 6 7 4
@@ -4108,20 +4151,20 @@
 0 4 2 5</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3864 (0.21%)
 ✅ iBet: 8/208 (3.85%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>3 9 9 3
 2 1 8 5
@@ -4129,20 +4172,20 @@
 4 7 6 7</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>30/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>9 8 0 8
 6 2 3 4
@@ -4150,20 +4193,20 @@
 4 6 1 7</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>0 6 5 3
 7 4 3 7
@@ -4171,20 +4214,20 @@
 9 2 9 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>2 5 8 9
 6 1 6 7
@@ -4192,20 +4235,20 @@
 1 4 4 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>7 6 0 7
 0 5 6 3
@@ -4213,20 +4256,20 @@
 9 2 1 2</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>2 9 3 6
 4 0 2 3
@@ -4234,20 +4277,20 @@
 8 6 1 7</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>4 2 7 0
 1 4 9 5
@@ -4255,20 +4298,20 @@
 8 5 0 3</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>6 4 0 9
 9 5 2 1
@@ -4276,20 +4319,20 @@
 0 3 5 2</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>5 7 9 8
 6 6 1 9
@@ -4297,20 +4340,20 @@
 8 0 4 3</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/3672 (0.22%)
 ✅ iBet: 8/195 (4.10%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>0 4 4 5
 2 8 0 2
@@ -4318,20 +4361,20 @@
 1 5 3 6</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4230 (0.38%)
 ✅ iBet: 16/221 (7.24%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>7 0 7 5
 8 2 4 8
@@ -4339,20 +4382,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4128 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>5 1 3 4
 6 2 2 7
@@ -4360,20 +4403,20 @@
 0 0 8 8</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4 7 0 3
 6 9 1 5
@@ -4381,20 +4424,20 @@
 5 8 9 7</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>2 0 6 8
 0 8 7 2
@@ -4402,20 +4445,20 @@
 1 3 4 5</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>5 6 6 2
 8 5 0 7
@@ -4423,20 +4466,20 @@
 9 8 9 4</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4302 (0.37%)
 ✅ iBet: 16/226 (7.08%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>1 6 4 3
 8 5 3 1
@@ -4444,20 +4487,20 @@
 0 8 5 7</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>9 7 3 7
 4 8 6 6
@@ -4465,20 +4508,20 @@
 2 4 0 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>1 9 7 0
 3 5 3 2
@@ -4486,20 +4529,20 @@
 6 7 4 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4212 (0.31%)
 ✅ iBet: 13/223 (5.83%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>3 3 9 4
 2 2 6 7
@@ -4507,20 +4550,20 @@
 1 0 7 8</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>0 3 5 8
 2 6 0 9
@@ -4528,20 +4571,20 @@
 4 5 4 7</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>1 4 1 4
 5 9 6 7
@@ -4549,20 +4592,20 @@
 6 5 0 2</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4176 (0.19%)
 ✅ iBet: 8/220 (3.64%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>0 9 9 7
 2 2 3 0
@@ -4570,20 +4613,20 @@
 7 8 1 6</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>7 6 9 1
 2 3 3 7
@@ -4591,20 +4634,20 @@
 9 8 1 4</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>3 2 5 1
 0 9 6 0
@@ -4612,20 +4655,20 @@
 5 8 4 4</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>0 9 6 8
 1 8 0 1
@@ -4633,20 +4676,20 @@
 3 3 7 5</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>5 7 1 3
 2 5 2 4
@@ -4654,20 +4697,20 @@
 3 9 6 8</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>2 6 1 7
 3 0 0 3
@@ -4675,20 +4718,20 @@
 6 8 9 5</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>9 5 2 6
 7 6 8 8
@@ -4696,20 +4739,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>1 5 6 3
 5 9 0 8
@@ -4717,20 +4760,20 @@
 9 8 7 2</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>1 9 9 6
 7 2 8 2
@@ -4738,20 +4781,20 @@
 6 0 3 4</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4212 (0.40%)
 ✅ iBet: 17/223 (7.62%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>2 3 5 5
 1 7 9 8
@@ -4759,20 +4802,20 @@
 6 9 4 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4302 (0.16%)
 ✅ iBet: 7/226 (3.10%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>9 7 8 7
 2 2 5 6
@@ -4780,20 +4823,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3828 (0.34%)
 ✅ iBet: 13/205 (6.34%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>6 8 1 4
 0 9 2 3
@@ -4801,20 +4844,20 @@
 9 3 5 7</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4176 (0.31%)
 ✅ iBet: 13/220 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>6 3 1 5
 3 0 6 9
@@ -4822,20 +4865,20 @@
 4 4 0 8</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/4302 (0.19%)
 ✅ iBet: 8/226 (3.54%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>4 0 8 9
 9 3 4 5
@@ -4843,20 +4886,20 @@
 2 6 3 7</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>5 0 7 5
 8 3 4 8
@@ -4864,20 +4907,20 @@
 0 1 2 9</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4128 (0.29%)
 ✅ iBet: 12/217 (5.53%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>2 1 7 3
 7 4 4 5
@@ -4885,20 +4928,20 @@
 9 0 0 8</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>1 1 9 6
 9 7 3 4
@@ -4906,20 +4949,20 @@
 2 2 4 5</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 0 7 6
 4 1 5 8
@@ -4927,20 +4970,20 @@
 2 9 1 3</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>2 1 6 2
 8 3 7 4
@@ -4948,20 +4991,20 @@
 5 4 5 9</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>8 8 3 6
 9 5 6 2
@@ -4969,20 +5012,20 @@
 7 4 9 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -4990,20 +5033,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>6 7 1 6
 0 1 2 3
@@ -5011,20 +5054,20 @@
 4 8 4 8</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4554 (0.29%)
 ✅ iBet: 13/237 (5.49%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>7 7 9 4
 3 8 4 8
@@ -5032,20 +5075,20 @@
 2 0 6 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>2 8 9 4
 6 4 6 7
@@ -5053,20 +5096,20 @@
 3 0 5 5</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>8 7 1 7
 2 5 4 5
@@ -5074,20 +5117,20 @@
 9 4 6 6</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>9 8 7 7
 4 3 8 5
@@ -5095,20 +5138,20 @@
 0 2 0 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/4302 (0.12%)
 ✅ iBet: 5/226 (2.21%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>5 8 7 8
 2 6 0 5
@@ -5116,20 +5159,20 @@
 3 7 4 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>1 0 6 6
 0 1 3 7
@@ -5137,20 +5180,20 @@
 7 5 2 9</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>0 9 7 1
 2 0 8 7
@@ -5158,20 +5201,20 @@
 5 4 4 3</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -5179,20 +5222,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -5200,20 +5243,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -5221,20 +5264,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -5242,20 +5285,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -5263,20 +5306,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -5284,20 +5327,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -5305,20 +5348,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -5326,20 +5369,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -5347,20 +5390,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -5368,20 +5411,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -5389,20 +5432,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -5410,20 +5453,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -5431,20 +5474,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -5452,20 +5495,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -5473,20 +5516,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -5494,20 +5537,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -5515,20 +5558,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -5536,20 +5579,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -5557,20 +5600,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -5578,20 +5621,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -5599,20 +5642,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -5620,20 +5663,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -5641,20 +5684,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -5662,20 +5705,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -5683,20 +5726,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -5704,20 +5747,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -5725,20 +5768,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -5746,20 +5789,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -5767,20 +5810,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -5788,20 +5831,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -5809,20 +5852,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -5830,20 +5873,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -5851,20 +5894,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -5872,20 +5915,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -5893,20 +5936,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -5914,20 +5957,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -5935,20 +5978,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -5956,20 +5999,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -5977,20 +6020,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -5998,20 +6041,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -6019,20 +6062,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -6040,20 +6083,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -6061,20 +6104,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -6082,20 +6125,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -6103,20 +6146,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -6124,20 +6167,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -6145,20 +6188,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -6166,20 +6209,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -6187,20 +6230,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -6208,20 +6251,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -6229,20 +6272,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -6250,20 +6293,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -6271,20 +6314,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -6292,20 +6335,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -6313,20 +6356,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -6334,20 +6377,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -6355,20 +6398,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -6376,20 +6419,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -6397,20 +6440,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -6418,20 +6461,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -6439,20 +6482,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -6460,20 +6503,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -6481,20 +6524,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -6502,20 +6545,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -6523,20 +6566,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -6544,20 +6587,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -6565,20 +6608,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -6586,20 +6629,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -6607,20 +6650,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -6628,20 +6671,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -6649,20 +6692,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -6670,20 +6713,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -6691,20 +6734,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -6712,20 +6755,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -6733,20 +6776,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -6754,20 +6797,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -6775,20 +6818,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -6796,20 +6839,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -6817,20 +6860,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" t="inlineStr">
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -6838,20 +6881,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" t="inlineStr">
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B144" s="11" t="inlineStr">
+      <c r="B145" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -6859,20 +6902,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" t="inlineStr">
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B145" s="11" t="inlineStr">
+      <c r="B146" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -6880,20 +6923,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" t="inlineStr">
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B146" s="11" t="inlineStr">
+      <c r="B147" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -6901,20 +6944,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" t="inlineStr">
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B147" s="11" t="inlineStr">
+      <c r="B148" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -6922,20 +6965,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B148" s="9" t="inlineStr">
+      <c r="B149" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -6943,20 +6986,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" t="inlineStr">
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -6964,20 +7007,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" t="inlineStr">
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -6985,20 +7028,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" t="inlineStr">
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B151" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -7006,20 +7049,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C152" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" t="inlineStr">
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -7027,20 +7070,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" t="inlineStr">
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -7048,20 +7091,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" t="inlineStr">
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -7069,20 +7112,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" t="inlineStr">
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -7090,20 +7133,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" t="inlineStr">
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -7111,20 +7154,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" t="inlineStr">
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -7132,20 +7175,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C158" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" t="inlineStr">
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -7153,20 +7196,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" t="inlineStr">
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -7174,20 +7217,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" t="inlineStr">
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -7195,20 +7238,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" t="inlineStr">
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -7216,20 +7259,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C162" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" t="inlineStr">
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -7237,20 +7280,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" t="inlineStr">
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -7258,20 +7301,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" t="inlineStr">
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -7279,20 +7322,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" t="inlineStr">
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -7300,20 +7343,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" t="inlineStr">
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -7321,20 +7364,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" t="inlineStr">
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -7342,20 +7385,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" t="inlineStr">
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -7363,20 +7406,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -7384,20 +7427,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C170" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -7405,20 +7448,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" t="inlineStr">
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -7426,20 +7469,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" t="inlineStr">
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -7447,20 +7490,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" t="inlineStr">
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -7468,20 +7511,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" t="inlineStr">
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -7489,20 +7532,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" t="inlineStr">
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -7510,20 +7553,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C176" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" t="inlineStr">
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -7531,20 +7574,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" t="inlineStr">
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -7552,20 +7595,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C178" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" t="inlineStr">
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -7573,20 +7616,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" t="inlineStr">
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -7594,20 +7637,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C180" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" t="inlineStr">
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -7615,20 +7658,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" t="inlineStr">
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -7636,20 +7679,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" t="inlineStr">
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B182" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -7657,20 +7700,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" t="inlineStr">
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -7678,20 +7721,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -7699,20 +7742,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" t="inlineStr">
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -7720,20 +7763,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C186" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" t="inlineStr">
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -7741,20 +7784,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" t="inlineStr">
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -7762,20 +7805,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" t="inlineStr">
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -7783,20 +7826,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" t="inlineStr">
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -7804,20 +7847,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C190" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" t="inlineStr">
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -7825,20 +7868,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" t="inlineStr">
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -7846,20 +7889,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" t="inlineStr">
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -7867,20 +7910,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" t="inlineStr">
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -7888,20 +7931,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C194" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" t="inlineStr">
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -7909,20 +7952,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" t="inlineStr">
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -7930,20 +7973,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" t="inlineStr">
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -7951,20 +7994,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="60" customHeight="1">
-      <c r="A197" t="inlineStr">
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -7972,20 +8015,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="60" customHeight="1">
-      <c r="A198" t="inlineStr">
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -7993,20 +8036,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="60" customHeight="1">
-      <c r="A199" t="inlineStr">
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B199" s="8" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -8014,20 +8057,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C199" s="1" t="inlineStr">
+      <c r="C200" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="60" customHeight="1">
-      <c r="A200" t="inlineStr">
+    <row r="201" ht="60" customHeight="1">
+      <c r="A201" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -8035,20 +8078,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C200" s="1" t="inlineStr">
+      <c r="C201" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="60" customHeight="1">
-      <c r="A201" t="inlineStr">
+    <row r="202" ht="60" customHeight="1">
+      <c r="A202" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B201" s="8" t="inlineStr">
+      <c r="B202" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -8056,20 +8099,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C201" s="1" t="inlineStr">
+      <c r="C202" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="60" customHeight="1">
-      <c r="A202" t="inlineStr">
+    <row r="203" ht="60" customHeight="1">
+      <c r="A203" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B202" s="8" t="inlineStr">
+      <c r="B203" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -8077,20 +8120,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C202" s="1" t="inlineStr">
+      <c r="C203" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="60" customHeight="1">
-      <c r="A203" t="inlineStr">
+    <row r="204" ht="60" customHeight="1">
+      <c r="A204" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B203" s="8" t="inlineStr">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -8098,20 +8141,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C203" s="1" t="inlineStr">
+      <c r="C204" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="60" customHeight="1">
-      <c r="A204" t="inlineStr">
+    <row r="205" ht="60" customHeight="1">
+      <c r="A205" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B204" s="8" t="inlineStr">
+      <c r="B205" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -8119,16 +8162,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C204" s="1" t="inlineStr">
+      <c r="C205" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="205">
-      <c r="B205" s="1" t="n"/>
-      <c r="C205" s="1" t="n"/>
     </row>
     <row r="206">
       <c r="B206" s="1" t="n"/>
@@ -8140,6 +8179,7 @@
     </row>
     <row r="208">
       <c r="B208" s="1" t="n"/>
+      <c r="C208" s="1" t="n"/>
     </row>
     <row r="209">
       <c r="B209" s="1" t="n"/>
@@ -8215,6 +8255,9 @@
     </row>
     <row r="233">
       <c r="B233" s="1" t="n"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04/10/2026 (Sun)</t>
+          <t>07/10/2026 (Wed)</t>
         </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
@@ -562,10 +562,32 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>04/10/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>4 7 1 6
+3 2 6 8
+1 5 3 9
+5 8 9 0</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 3/220 (1.36%)
+▶ Direct: 3/4176 (0.07%)
+▶ Total Sets hit: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>03/10/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -573,7 +595,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 10/4230 (0.24%)
@@ -581,13 +603,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>30/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -595,7 +617,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 2/221 (0.90%)
 ▶ Direct: 2/4230 (0.05%)
@@ -603,13 +625,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>27/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -617,7 +639,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -625,13 +647,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>26/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 5
@@ -639,7 +661,7 @@
 4 8 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -647,13 +669,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>23/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -661,7 +683,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/221 (4.52%)
 ▶ Direct: 10/4230 (0.24%)
@@ -669,13 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>20/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -683,7 +705,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -691,13 +713,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>19/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -705,7 +727,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/220 (5.91%)
 ▶ Direct: 13/4176 (0.31%)
@@ -713,13 +735,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>16/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>4 7 1 6
 3 2 6 7
@@ -727,7 +749,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/220 (6.82%)
 ▶ Direct: 15/4176 (0.36%)
@@ -735,13 +757,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>13/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -749,7 +771,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -757,13 +779,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>12/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 3 2 6 7
@@ -771,7 +793,7 @@
 5 8 9 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -779,13 +801,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>09/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -793,7 +815,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -801,13 +823,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>06/09/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -815,7 +837,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/217 (3.69%)
 ▶ Direct: 8/4128 (0.19%)
@@ -823,13 +845,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>05/09/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -837,7 +859,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/217 (1.84%)
 ▶ Direct: 4/4128 (0.10%)
@@ -845,13 +867,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>02/09/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>0 7 1 6
 2 8 6 7
@@ -859,7 +881,7 @@
 5 2 9 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/217 (3.23%)
 ▶ Direct: 7/4128 (0.17%)
@@ -867,13 +889,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>29/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -881,7 +903,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -889,13 +911,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>26/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -903,7 +925,7 @@
 5 9 0 3</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/196 (2.04%)
 ▶ Direct: 4/3606 (0.11%)
@@ -911,13 +933,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>23/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -925,7 +947,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/223 (2.69%)
 ▶ Direct: 6/4212 (0.14%)
@@ -933,13 +955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>22/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -947,7 +969,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -955,13 +977,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>19/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -969,7 +991,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -977,13 +999,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>16/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -991,7 +1013,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -999,13 +1021,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>15/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1013,7 +1035,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1021,13 +1043,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>12/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1035,7 +1057,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1043,13 +1065,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>09/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1057,7 +1079,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1065,13 +1087,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>08/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1079,7 +1101,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/209 (4.31%)
 ▶ Direct: 9/3936 (0.23%)
@@ -1087,13 +1109,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>05/08/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1101,7 +1123,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/209 (6.22%)
 ▶ Direct: 13/3936 (0.33%)
@@ -1109,13 +1131,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>02/08/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1123,7 +1145,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/209 (6.70%)
 ▶ Direct: 14/3936 (0.36%)
@@ -1131,13 +1153,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>01/08/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1145,7 +1167,7 @@
 5 4 0 3</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1153,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>29/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 6 8
@@ -1167,7 +1189,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/209 (3.35%)
 ▶ Direct: 7/3936 (0.18%)
@@ -1175,13 +1197,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>26/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1189,7 +1211,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1197,13 +1219,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>25/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 8
@@ -1211,7 +1233,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1219,13 +1241,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>22/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1233,7 +1255,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/221 (3.62%)
 ▶ Direct: 8/4230 (0.19%)
@@ -1241,13 +1263,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>19/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>6 4 1 7
 0 2 8 3
@@ -1255,7 +1277,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/221 (6.33%)
 ▶ Direct: 14/4230 (0.33%)
@@ -1263,13 +1285,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>18/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1277,7 +1299,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1285,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>15/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1299,7 +1321,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/226 (6.19%)
 ▶ Direct: 14/4302 (0.33%)
@@ -1307,13 +1329,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>12/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1321,7 +1343,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1329,13 +1351,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>11/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1343,7 +1365,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1351,13 +1373,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>08/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1365,7 +1387,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1373,13 +1395,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>05/07/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1387,7 +1409,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/217 (5.53%)
 ▶ Direct: 12/4128 (0.29%)
@@ -1395,13 +1417,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>04/07/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 8 3
@@ -1409,7 +1431,7 @@
 5 4 9 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1417,13 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>01/07/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 8
@@ -1431,7 +1453,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1439,13 +1461,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>28/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1453,7 +1475,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1461,13 +1483,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>27/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>3 7 1 6
 0 2 4 8
@@ -1475,7 +1497,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1483,13 +1505,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>24/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>8 7 1 6
 0 2 4 3
@@ -1497,7 +1519,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1505,13 +1527,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>21/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 3
@@ -1519,7 +1541,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1527,13 +1549,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>20/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 4 8
@@ -1541,7 +1563,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1549,13 +1571,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>17/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1563,7 +1585,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1571,13 +1593,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>14/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1585,7 +1607,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1593,13 +1615,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>13/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 8
@@ -1607,7 +1629,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1615,13 +1637,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>10/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1629,7 +1651,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/223 (4.04%)
 ▶ Direct: 9/4212 (0.21%)
@@ -1637,13 +1659,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>07/06/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1651,7 +1673,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/223 (4.48%)
 ▶ Direct: 10/4212 (0.24%)
@@ -1659,13 +1681,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>06/06/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1673,7 +1695,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/223 (4.93%)
 ▶ Direct: 11/4212 (0.26%)
@@ -1681,13 +1703,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>03/06/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1695,7 +1717,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/223 (3.14%)
 ▶ Direct: 7/4212 (0.17%)
@@ -1703,13 +1725,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>31/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 3
@@ -1717,7 +1739,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1725,13 +1747,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>30/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1739,7 +1761,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1747,13 +1769,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>27/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1761,7 +1783,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/220 (4.55%)
 ▶ Direct: 10/4176 (0.24%)
@@ -1769,13 +1791,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>24/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1783,7 +1805,7 @@
 5 6 0 3</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1791,13 +1813,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>23/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1805,7 +1827,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1813,13 +1835,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>20/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1827,7 +1849,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1835,13 +1857,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>17/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1849,7 +1871,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/217 (4.15%)
 ▶ Direct: 9/4128 (0.22%)
@@ -1857,13 +1879,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>16/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1871,7 +1893,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -1879,13 +1901,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>13/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1893,7 +1915,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -1901,13 +1923,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>10/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1915,7 +1937,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
@@ -1923,13 +1945,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1937,7 +1959,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -1945,13 +1967,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="14" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1959,7 +1981,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1967,13 +1989,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -1981,7 +2003,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1989,13 +2011,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="14" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -2003,7 +2025,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2011,13 +2033,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      